--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
@@ -32071,7 +32071,8 @@
 MSG-PM-073: "Compile the comparative master first" (COMPARATIVE_NO_MASTER)
 MSG-PM-074: "Send the quotation slip of round &lt;round no&gt; first" (COMPARATIVE_NO_TERMS)
 MSG-PM-075: "Enter the title of the view" (COMPARATIVE_TITLE_REQUIRED)
-MSG-PM-076: "Comparative output not found: &lt;output id&gt;" (NOT_FOUND)</t>
+MSG-PM-076: "Comparative output not found: &lt;output id&gt;" (NOT_FOUND)
+MSG-PM-077: "Select the ManCom approvers; the request is signed off when all of them approved" (PKG_MANCOM_ROUTING)</t>
         </is>
       </c>
       <c r="L258" s="12" t="inlineStr">
@@ -32156,9 +32157,9 @@
       <c r="K259" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-079: "The package end date must be after the effective date" (PKG_DATES_INVALID)
-MSG-PM-080: "ManCom signs off requirements submitted by someone else" (PKG_FOUR_EYES)
-MSG-PM-081: "Complete the requirements: &lt;missing&gt;" (REQUIREMENTS_INCOMPLETE)</t>
+MSG-PM-080: "The package end date must be after the effective date" (PKG_DATES_INVALID)
+MSG-PM-081: "ManCom signs off requirements submitted by someone else" (PKG_FOUR_EYES)
+MSG-PM-082: "Complete the requirements: &lt;missing&gt;" (REQUIREMENTS_INCOMPLETE)</t>
         </is>
       </c>
       <c r="L259" s="12" t="inlineStr">
@@ -32243,23 +32244,23 @@
       <c r="K260" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-084: "The advisory was already sent" (ADVISORY_ALREADY_SENT)
-MSG-PM-085: "Enter the subject and the text" (ADVISORY_CONTENT_REQUIRED)
-MSG-PM-086: "Attach the supporting documents before sending: &lt;missing&gt;" (ADVISORY_DOCUMENTS_MISSING)
-MSG-PM-087: "Select at least one recipient group" (ADVISORY_NO_RECIPIENT)
-MSG-PM-088: "Product already exists: &lt;key&gt;" (DUPLICATE)
-MSG-PM-089: "Package advisory not found: &lt;advisory id&gt;" (NOT_FOUND)
-MSG-PM-090: "Package version not found: &lt;version no&gt;" (NOT_FOUND)
-MSG-PM-091: "Insurer &lt;insurer code&gt; has terms but is not on the package" (PACKAGE_TERM_INSURER_UNKNOWN)
-MSG-PM-092: "A retirement request retires the package; it has no version to set up" (PKG_REQUEST_TYPE_MISMATCH)
-MSG-PM-093: "Only a request to retire the package can retire it" (PKG_REQUEST_TYPE_MISMATCH)
-MSG-PM-094: "Enter the product code" (PRODUCT_CODE_REQUIRED)
-MSG-PM-095: "Enter the risk code of the new package" (PRODUCT_CODE_REQUIRED)
-MSG-PM-096: "Product &lt;product code&gt; is &lt;lifecycle status&gt; already" (PRODUCT_NOT_ACTIVE)
-MSG-PM-097: "Product &lt;product code&gt; is not a package" (PRODUCT_NOT_PACKAGED)
-MSG-PM-098: "Product &lt;product code&gt; has no version" (PRODUCT_NOT_VERSIONED)
-MSG-PM-099: "Product &lt;code&gt; already has a version being set up" (VERSION_IN_PROGRESS)
-MSG-PM-100: "The content is for product &lt;product code&gt;" (VERSION_PRODUCT_MISMATCH)</t>
+MSG-PM-085: "The advisory was already sent" (ADVISORY_ALREADY_SENT)
+MSG-PM-086: "Enter the subject and the text" (ADVISORY_CONTENT_REQUIRED)
+MSG-PM-087: "Attach the supporting documents before sending: &lt;missing&gt;" (ADVISORY_DOCUMENTS_MISSING)
+MSG-PM-088: "Select at least one recipient group" (ADVISORY_NO_RECIPIENT)
+MSG-PM-089: "Product already exists: &lt;key&gt;" (DUPLICATE)
+MSG-PM-090: "Package advisory not found: &lt;advisory id&gt;" (NOT_FOUND)
+MSG-PM-091: "Package version not found: &lt;version no&gt;" (NOT_FOUND)
+MSG-PM-092: "Insurer &lt;insurer code&gt; has terms but is not on the package" (PACKAGE_TERM_INSURER_UNKNOWN)
+MSG-PM-093: "A retirement request retires the package; it has no version to set up" (PKG_REQUEST_TYPE_MISMATCH)
+MSG-PM-094: "Only a request to retire the package can retire it" (PKG_REQUEST_TYPE_MISMATCH)
+MSG-PM-095: "Enter the product code" (PRODUCT_CODE_REQUIRED)
+MSG-PM-096: "Enter the risk code of the new package" (PRODUCT_CODE_REQUIRED)
+MSG-PM-097: "Product &lt;product code&gt; is &lt;lifecycle status&gt; already" (PRODUCT_NOT_ACTIVE)
+MSG-PM-098: "Product &lt;product code&gt; is not a package" (PRODUCT_NOT_PACKAGED)
+MSG-PM-099: "Product &lt;product code&gt; has no version" (PRODUCT_NOT_VERSIONED)
+MSG-PM-100: "Product &lt;code&gt; already has a version being set up" (VERSION_IN_PROGRESS)
+MSG-PM-101: "The content is for product &lt;product code&gt;" (VERSION_PRODUCT_MISMATCH)</t>
         </is>
       </c>
       <c r="L260" s="12" t="inlineStr">
@@ -32344,9 +32345,9 @@
       <c r="K261" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-103: "Select the company" (COMPANY_REQUIRED)
-MSG-PM-104: "Released package not found: &lt;code&gt;" (NOT_FOUND)
-MSG-PM-105: "Select the packages to renew" (PKG_RENEWAL_NONE)</t>
+MSG-PM-104: "Select the company" (COMPANY_REQUIRED)
+MSG-PM-105: "Released package not found: &lt;code&gt;" (NOT_FOUND)
+MSG-PM-106: "Select the packages to renew" (PKG_RENEWAL_NONE)</t>
         </is>
       </c>
       <c r="L261" s="12" t="inlineStr">
@@ -32431,21 +32432,21 @@
       <c r="K262" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-108: "The risk-code pattern is not a valid regular expression" (CODE_PATTERN_INVALID)
-MSG-PM-109: "A subtype cannot have subtypes (Type &gt; Subtype only)" (COVER_TYPE_DEPTH)
-MSG-PM-110: "Cover type &lt;cover type code&gt; does not belong to &lt;line code&gt;" (COVER_TYPE_INVALID)
-MSG-PM-111: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-PM-112: "&lt;label&gt; not found: &lt;code&gt;" (NOT_FOUND)
-MSG-PM-113: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-PM-114: "&lt;label&gt; not found: &lt;parent code&gt;" (NOT_FOUND)
-MSG-PM-115: "A package needs its cover type" (PACKAGE_HIERARCHY_INCOMPLETE)
-MSG-PM-116: "Risk code &lt;code&gt; does not follow the naming convention of &lt;line code&gt;" (PRODUCT_CODE_PATTERN)
-MSG-PM-117: "The rate, minimum premium, commission and TSI limit of package &lt;code&gt; change through a new version (Versions tab)" (PRODUCT_FIELD_VERSIONED)
-MSG-PM-118: "The minimum premium cannot be negative" (PRODUCT_MINIMUM_INVALID)
-MSG-PM-119: "Product &lt;code&gt; is not authorized or is inactive" (PRODUCT_NOT_ACTIVE)
-MSG-PM-120: "Package &lt;code&gt; has no released version in force on &lt;date&gt;" (PRODUCT_NOT_SELLABLE)
-MSG-PM-121: "Product &lt;code&gt; is &lt;root&gt; and cannot be sold" (PRODUCT_NOT_SELLABLE)
-MSG-PM-122: "The maximum term must be between 1 and 10 years" (PRODUCT_TERM_INVALID)</t>
+MSG-PM-109: "The risk-code pattern is not a valid regular expression" (CODE_PATTERN_INVALID)
+MSG-PM-110: "A subtype cannot have subtypes (Type &gt; Subtype only)" (COVER_TYPE_DEPTH)
+MSG-PM-111: "Cover type &lt;cover type code&gt; does not belong to &lt;line code&gt;" (COVER_TYPE_INVALID)
+MSG-PM-112: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-PM-113: "&lt;label&gt; not found: &lt;code&gt;" (NOT_FOUND)
+MSG-PM-114: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-PM-115: "&lt;label&gt; not found: &lt;parent code&gt;" (NOT_FOUND)
+MSG-PM-116: "A package needs its cover type" (PACKAGE_HIERARCHY_INCOMPLETE)
+MSG-PM-117: "Risk code &lt;code&gt; does not follow the naming convention of &lt;line code&gt;" (PRODUCT_CODE_PATTERN)
+MSG-PM-118: "The rate, minimum premium, commission and TSI limit of package &lt;code&gt; change through a new version (Versions tab)" (PRODUCT_FIELD_VERSIONED)
+MSG-PM-119: "The minimum premium cannot be negative" (PRODUCT_MINIMUM_INVALID)
+MSG-PM-120: "Product &lt;code&gt; is not authorized or is inactive" (PRODUCT_NOT_ACTIVE)
+MSG-PM-121: "Package &lt;code&gt; has no released version in force on &lt;date&gt;" (PRODUCT_NOT_SELLABLE)
+MSG-PM-122: "Product &lt;code&gt; is &lt;root&gt; and cannot be sold" (PRODUCT_NOT_SELLABLE)
+MSG-PM-123: "The maximum term must be between 1 and 10 years" (PRODUCT_TERM_INVALID)</t>
         </is>
       </c>
       <c r="L262" s="12" t="inlineStr">
@@ -32530,12 +32531,12 @@
       <c r="K263" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-123: "Describe the change"
-MSG-PM-129: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-PM-130: "Complete the parameters of the &lt;type&gt; rule" (FIELD_RULE_INCOMPLETE)
-MSG-PM-131: "Unknown list of values &lt;lov type&gt;" (LOV_TYPE_UNKNOWN)
-MSG-PM-132: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-PM-133: "Rules for every product use the scope code '*'" (RULE_SCOPE_INVALID)</t>
+MSG-PM-124: "Describe the change"
+MSG-PM-130: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-PM-131: "Complete the parameters of the &lt;type&gt; rule" (FIELD_RULE_INCOMPLETE)
+MSG-PM-132: "Unknown list of values &lt;lov type&gt;" (LOV_TYPE_UNKNOWN)
+MSG-PM-133: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-PM-134: "Rules for every product use the scope code '*'" (RULE_SCOPE_INVALID)</t>
         </is>
       </c>
       <c r="L263" s="12" t="inlineStr">
@@ -32620,29 +32621,30 @@
       <c r="K264" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-135: "Correct the highlighted fields"
-MSG-PM-136: "Enter a commission between 0 and 100"
-MSG-PM-137: "Enter a positive amount"
-MSG-PM-138: "Enter a rate between 0 and 100"
-MSG-PM-139: "Enter the effective date"
-MSG-PM-140: "Enter the minimum premium"
-MSG-PM-141: "Enter the package rate or a rate for every insurer"
-MSG-PM-142: "Include at least one coverage"
-MSG-PM-146: "The effective date cannot be before today"
-MSG-PM-147: "The package end date must be after the effective date"
-MSG-PM-148: "The package version is validated and released for use."
-MSG-PM-151: "A package version is validated by someone other than its maker and submitter" (MAKER_CHECKER_VIOLATION)
-MSG-PM-152: "Package version not found: &lt;version no&gt;" (NOT_FOUND)
-MSG-PM-153: "Enter the effective date" (PACKAGE_DATES_INVALID)
-MSG-PM-154: "The effective date cannot be before today" (PACKAGE_DATES_INVALID)
-MSG-PM-155: "The effective date must be after the start of version &lt;version no&gt;" (PACKAGE_DATES_INVALID)
-MSG-PM-156: "The package end date must be after the effective date" (PACKAGE_DATES_INVALID)
-MSG-PM-157: "The package needs its cover type and at least one included basic coverage" (PACKAGE_HIERARCHY_INCOMPLETE)
-MSG-PM-158: "Insurer &lt;insurer code&gt; has no terms for coverage &lt;coverage&gt;" (PACKAGE_INSURER_TERMS_MISSING)
-MSG-PM-159: "Enter the package rate or a rate for every insurer" (PACKAGE_RATE_MISSING)
-MSG-PM-160: "The co-insurance shares must add up to 100%" (PACKAGE_SHARES_INVALID)
-MSG-PM-161: "Enter the reason of the return" (REASON_REQUIRED)
-MSG-PM-162: "Version &lt;version no&gt; is &lt;status&gt;" (VERSION_NOT_FOR_VALIDATION)</t>
+MSG-PM-136: "Correct the highlighted fields"
+MSG-PM-137: "Enter a commission between 0 and 100"
+MSG-PM-138: "Enter a positive amount"
+MSG-PM-139: "Enter a rate between 0 and 100"
+MSG-PM-140: "Enter the effective date"
+MSG-PM-141: "Enter the minimum premium"
+MSG-PM-142: "Enter the package rate or a rate for every insurer"
+MSG-PM-143: "Include at least one coverage"
+MSG-PM-147: "The effective date cannot be before today"
+MSG-PM-148: "The package end date must be after the effective date"
+MSG-PM-149: "The package version is validated and released for use."
+MSG-PM-152: "A package version is validated by someone other than its maker and submitter" (MAKER_CHECKER_VIOLATION)
+MSG-PM-153: "Package version not found: &lt;version no&gt;" (NOT_FOUND)
+MSG-PM-154: "Enter the effective date" (PACKAGE_DATES_INVALID)
+MSG-PM-155: "The effective date cannot be before today" (PACKAGE_DATES_INVALID)
+MSG-PM-156: "The effective date must be after the start of version &lt;version no&gt;" (PACKAGE_DATES_INVALID)
+MSG-PM-157: "The package end date must be after the effective date" (PACKAGE_DATES_INVALID)
+MSG-PM-158: "The package needs its cover type and at least one included basic coverage" (PACKAGE_HIERARCHY_INCOMPLETE)
+MSG-PM-159: "Insurer &lt;insurer code&gt; has no terms for coverage &lt;coverage&gt;" (PACKAGE_INSURER_TERMS_MISSING)
+MSG-PM-160: "Enter the package rate or a rate for every insurer" (PACKAGE_RATE_MISSING)
+MSG-PM-161: "The co-insurance shares must add up to 100%" (PACKAGE_SHARES_INVALID)
+MSG-PM-162: "The expiry date must be after the package start date &lt;package start date&gt;" (PKG_DEACTIVATION_DATE)
+MSG-PM-163: "Enter the reason of the return" (REASON_REQUIRED)
+MSG-PM-164: "Version &lt;version no&gt; is &lt;status&gt;" (VERSION_NOT_FOR_VALIDATION)</t>
         </is>
       </c>
       <c r="L264" s="12" t="inlineStr">
@@ -32727,17 +32729,17 @@
       <c r="K265" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-166: "Enter the effective date"
-MSG-PM-167: "Enter the name"
-MSG-PM-168: "Enter the title"
-MSG-PM-169: "Enter the wording"
-MSG-PM-171: "Select the kind"
-MSG-PM-172: "Select the product line"
-MSG-PM-174: "The end is before the start"
-MSG-PM-175: "Use A-Z, 0-9 and _"
-MSG-PM-176: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-PM-177: "&lt;label&gt; not found: &lt;code&gt;" (NOT_FOUND)
-MSG-PM-178: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-PM-168: "Enter the effective date"
+MSG-PM-169: "Enter the name"
+MSG-PM-170: "Enter the title"
+MSG-PM-171: "Enter the wording"
+MSG-PM-173: "Select the kind"
+MSG-PM-174: "Select the product line"
+MSG-PM-176: "The end is before the start"
+MSG-PM-177: "Use A-Z, 0-9 and _"
+MSG-PM-178: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-PM-179: "&lt;label&gt; not found: &lt;code&gt;" (NOT_FOUND)
+MSG-PM-180: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="L265" s="12" t="inlineStr">
@@ -32822,25 +32824,25 @@
       <c r="K266" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-181: "Enter a value for each parameter"
-MSG-PM-182: "Enter the name"
-MSG-PM-183: "Enter the start date"
-MSG-PM-184: "Enter the value"
-MSG-PM-186: "Select at least one product of the matrix"
-MSG-PM-187: "Select the parameter"
-MSG-PM-188: "Select the type"
-MSG-PM-189: "The change must start after &lt;active from&gt;"
-MSG-PM-190: "The end is before the start"
-MSG-PM-191: "Use A-Z, 0-9, _ and -"
-MSG-PM-192: "An active criterion is changed by amending it (successor)" (INCENTIVE_ACTIVE_LOCKED)
-MSG-PM-193: "Only an active criterion is amended; change the pending row" (INCENTIVE_NOT_ACTIVE)
-MSG-PM-194: "The amendment must start after &lt;effective from&gt;" (INCENTIVE_PERIOD_INVALID)
-MSG-PM-195: "Criterion &lt;code&gt; already covers part of this period" (INCENTIVE_PERIOD_OVERLAP)
-MSG-PM-196: "Select at least one product of the products matrix" (INCENTIVE_PRODUCTS_REQUIRED)
-MSG-PM-197: "Product &lt;product code&gt; is not an active product of the matrix" (INCENTIVE_PRODUCT_NOT_ACTIVE)
-MSG-PM-198: "Enter the rule parameters as parameter and value rows" (INCENTIVE_RULE_PARAMS_INVALID)
-MSG-PM-199: "Enter the value of the incentive criterion" (INCENTIVE_VALUE_REQUIRED)
-MSG-PM-200: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-PM-183: "Enter a value for each parameter"
+MSG-PM-184: "Enter the name"
+MSG-PM-185: "Enter the start date"
+MSG-PM-186: "Enter the value"
+MSG-PM-188: "Select at least one product of the matrix"
+MSG-PM-189: "Select the parameter"
+MSG-PM-190: "Select the type"
+MSG-PM-191: "The change must start after &lt;active from&gt;"
+MSG-PM-192: "The end is before the start"
+MSG-PM-193: "Use A-Z, 0-9, _ and -"
+MSG-PM-194: "An active criterion is changed by amending it (successor)" (INCENTIVE_ACTIVE_LOCKED)
+MSG-PM-195: "Only an active criterion is amended; change the pending row" (INCENTIVE_NOT_ACTIVE)
+MSG-PM-196: "The amendment must start after &lt;effective from&gt;" (INCENTIVE_PERIOD_INVALID)
+MSG-PM-197: "Criterion &lt;code&gt; already covers part of this period" (INCENTIVE_PERIOD_OVERLAP)
+MSG-PM-198: "Select at least one product of the products matrix" (INCENTIVE_PRODUCTS_REQUIRED)
+MSG-PM-199: "Product &lt;product code&gt; is not an active product of the matrix" (INCENTIVE_PRODUCT_NOT_ACTIVE)
+MSG-PM-200: "Enter the rule parameters as parameter and value rows" (INCENTIVE_RULE_PARAMS_INVALID)
+MSG-PM-201: "Enter the value of the incentive criterion" (INCENTIVE_VALUE_REQUIRED)
+MSG-PM-202: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="L266" s="12" t="inlineStr">
@@ -32925,17 +32927,17 @@
       <c r="K267" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-203: "Default credit days must be between 0 and 365" (CREDIT_DAYS_INVALID)
-MSG-PM-204: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-PM-205: "Branch &lt;branch code&gt; is not authorized or inactive" (INSURER_BRANCH_NOT_ACTIVE)
-MSG-PM-206: "Insurer &lt;party code&gt; has no branch &lt;branch code&gt;" (INSURER_BRANCH_UNKNOWN)
-MSG-PM-207: "Insurer &lt;party code&gt; is not authorized or is inactive" (INSURER_NOT_ACTIVE)
-MSG-PM-208: "&lt;label&gt; not found: &lt;branch id&gt;" (NOT_FOUND)
-MSG-PM-209: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-PM-210: "&lt;label&gt; not found: &lt;party code&gt;" (NOT_FOUND)
-MSG-PM-211: "Party &lt;party code&gt; exists and is not an insurer" (PARTY_NOT_INSURER)
-MSG-PM-212: "Only e-mail placement is available; choose the e-mail placement channel" (PLACEMENT_CHANNEL_PARKED)
-MSG-PM-213: "The LGT rate must be between 0 and 100 %" (RATE_INVALID)</t>
+MSG-PM-205: "Default credit days must be between 0 and 365" (CREDIT_DAYS_INVALID)
+MSG-PM-206: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-PM-207: "Branch &lt;branch code&gt; is not authorized or inactive" (INSURER_BRANCH_NOT_ACTIVE)
+MSG-PM-208: "Insurer &lt;party code&gt; has no branch &lt;branch code&gt;" (INSURER_BRANCH_UNKNOWN)
+MSG-PM-209: "Insurer &lt;party code&gt; is not authorized or is inactive" (INSURER_NOT_ACTIVE)
+MSG-PM-210: "&lt;label&gt; not found: &lt;branch id&gt;" (NOT_FOUND)
+MSG-PM-211: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-PM-212: "&lt;label&gt; not found: &lt;party code&gt;" (NOT_FOUND)
+MSG-PM-213: "Party &lt;party code&gt; exists and is not an insurer" (PARTY_NOT_INSURER)
+MSG-PM-214: "Only e-mail placement is available; choose the e-mail placement channel" (PLACEMENT_CHANNEL_PARKED)
+MSG-PM-215: "The LGT rate must be between 0 and 100 %" (RATE_INVALID)</t>
         </is>
       </c>
       <c r="L267" s="12" t="inlineStr">
@@ -33020,13 +33022,13 @@
       <c r="K268" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-217: "Enter the effective-from date" (EFFECTIVE_FROM_REQUIRED)
-MSG-PM-218: "The effective-to date is before the effective-from date" (EFFECTIVITY_INVALID)
-MSG-PM-219: "The limit must be greater than zero" (LIMIT_INVALID)
-MSG-PM-220: "The premium cannot be negative" (LIMIT_PREMIUM_INVALID)
-MSG-PM-221: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-PM-222: "&lt;label&gt; must be a percentage between 0 and 100" (RATE_INVALID)
-MSG-PM-223: "Months covered must be between 1 and 12" (SHORT_PERIOD_MONTHS_INVALID)</t>
+MSG-PM-219: "Enter the effective-from date" (EFFECTIVE_FROM_REQUIRED)
+MSG-PM-220: "The effective-to date is before the effective-from date" (EFFECTIVITY_INVALID)
+MSG-PM-221: "The limit must be greater than zero" (LIMIT_INVALID)
+MSG-PM-222: "The premium cannot be negative" (LIMIT_PREMIUM_INVALID)
+MSG-PM-223: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-PM-224: "&lt;label&gt; must be a percentage between 0 and 100" (RATE_INVALID)
+MSG-PM-225: "Months covered must be between 1 and 12" (SHORT_PERIOD_MONTHS_INVALID)</t>
         </is>
       </c>
       <c r="L268" s="12" t="inlineStr">
@@ -33103,19 +33105,19 @@
       <c r="K269" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-231: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-PM-232: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-PM-233: "&lt;label&gt; not found: &lt;unit code&gt;" (NOT_FOUND)
-MSG-PM-234: "Enter the reason" (REASON_REQUIRED)
-MSG-PM-235: "&lt;&gt; is already removed from the team" (SALES_OFFICER_INACTIVE)
-MSG-PM-236: "A &lt;level&gt; must belong to an active &lt;parent level&gt;" (SALES_PARENT_INVALID)
-MSG-PM-237: "Reactivate &lt;parent code&gt; before &lt;code&gt;" (SALES_PARENT_INVALID)
-MSG-PM-238: "Team &lt;team code&gt; is unknown or inactive" (SALES_TEAM_UNKNOWN)
-MSG-PM-239: "Unit &lt;code&gt; is already inactive" (SALES_UNIT_INACTIVE)
-MSG-PM-240: "&lt;code&gt; still has &lt;open&gt;: deactivate or move them before deactivating the unit" (SALES_UNIT_IN_USE)
-MSG-PM-241: "Unit &lt;code&gt; is not inactive" (SALES_UNIT_NOT_INACTIVE)
-MSG-PM-242: "Unknown user &lt;head&gt;" (USER_UNKNOWN)
-MSG-PM-243: "Unknown user &lt;username&gt;" (USER_UNKNOWN)</t>
+MSG-PM-233: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-PM-234: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-PM-235: "&lt;label&gt; not found: &lt;unit code&gt;" (NOT_FOUND)
+MSG-PM-236: "Enter the reason" (REASON_REQUIRED)
+MSG-PM-237: "&lt;&gt; is already removed from the team" (SALES_OFFICER_INACTIVE)
+MSG-PM-238: "A &lt;level&gt; must belong to an active &lt;parent level&gt;" (SALES_PARENT_INVALID)
+MSG-PM-239: "Reactivate &lt;parent code&gt; before &lt;code&gt;" (SALES_PARENT_INVALID)
+MSG-PM-240: "Team &lt;team code&gt; is unknown or inactive" (SALES_TEAM_UNKNOWN)
+MSG-PM-241: "Unit &lt;code&gt; is already inactive" (SALES_UNIT_INACTIVE)
+MSG-PM-242: "&lt;code&gt; still has &lt;open&gt;: deactivate or move them before deactivating the unit" (SALES_UNIT_IN_USE)
+MSG-PM-243: "Unit &lt;code&gt; is not inactive" (SALES_UNIT_NOT_INACTIVE)
+MSG-PM-244: "Unknown user &lt;head&gt;" (USER_UNKNOWN)
+MSG-PM-245: "Unknown user &lt;username&gt;" (USER_UNKNOWN)</t>
         </is>
       </c>
       <c r="L269" s="12" t="inlineStr">
@@ -33200,18 +33202,18 @@
       <c r="K270" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-244: "Insurer &lt;insurer code&gt; is not on the panel of &lt;product code&gt; version &lt;version no&gt;" (INSURER_NOT_ON_PACKAGE)
-MSG-PM-245: "&lt;coverage&gt; limit &lt;to plain string&gt; is not in the limit table" (MOTOR_LIMIT_UNKNOWN)
-MSG-PM-246: "Package &lt;code&gt; expired and has no current version" (PRODUCT_NOT_SELLABLE)
-MSG-PM-247: "Package &lt;code&gt; has no released version in force" (PRODUCT_NOT_SELLABLE)
-MSG-PM-248: "Package &lt;code&gt; is &lt;lifecycle status&gt;: it is locked for new business" (PRODUCT_NOT_SELLABLE)
-MSG-PM-249: "Enter at least one item to rate" (RATING_NO_ITEMS)
-MSG-PM-250: "The motor OD/Theft coverage factor is not set up" (RATING_OD_FACTOR_MISSING)
-MSG-PM-251: "The period end must be after the period start" (RATING_PERIOD_INVALID)
-MSG-PM-252: "Enter the premium rate of &lt;item&gt;" (RATING_RATE_REQUIRED)
-MSG-PM-253: "No short-period percentage applies to this period" (RATING_SHORT_PERIOD_INVALID)
-MSG-PM-254: "Enter a sum insured of zero or more for every item" (RATING_SUM_INSURED_INVALID)
-MSG-PM-255: "No short-period rate is set up for &lt;months&gt; month(s)" (SHORT_PERIOD_RATE_MISSING)</t>
+MSG-PM-246: "Insurer &lt;insurer code&gt; is not on the panel of &lt;product code&gt; version &lt;version no&gt;" (INSURER_NOT_ON_PACKAGE)
+MSG-PM-247: "&lt;coverage&gt; limit &lt;to plain string&gt; is not in the limit table" (MOTOR_LIMIT_UNKNOWN)
+MSG-PM-248: "Package &lt;code&gt; expired and has no current version" (PRODUCT_NOT_SELLABLE)
+MSG-PM-249: "Package &lt;code&gt; has no released version in force" (PRODUCT_NOT_SELLABLE)
+MSG-PM-250: "Package &lt;code&gt; is &lt;lifecycle status&gt;: it is locked for new business" (PRODUCT_NOT_SELLABLE)
+MSG-PM-251: "Enter at least one item to rate" (RATING_NO_ITEMS)
+MSG-PM-252: "The motor OD/Theft coverage factor is not set up" (RATING_OD_FACTOR_MISSING)
+MSG-PM-253: "The period end must be after the period start" (RATING_PERIOD_INVALID)
+MSG-PM-254: "Enter the premium rate of &lt;item&gt;" (RATING_RATE_REQUIRED)
+MSG-PM-255: "No short-period percentage applies to this period" (RATING_SHORT_PERIOD_INVALID)
+MSG-PM-256: "Enter a sum insured of zero or more for every item" (RATING_SUM_INSURED_INVALID)
+MSG-PM-257: "No short-period rate is set up for &lt;months&gt; month(s)" (SHORT_PERIOD_RATE_MISSING)</t>
         </is>
       </c>
       <c r="L270" s="12" t="inlineStr">
@@ -33296,14 +33298,14 @@
       <c r="K271" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-257: "A rate exception is decided by someone other than its requester" (MAKER_CHECKER_VIOLATION)
-MSG-PM-258: "&lt;label&gt; not found: &lt;reference&gt;" (NOT_FOUND)
-MSG-PM-259: "Only package rate schemes need an exception" (PRODUCT_NOT_PACKAGED)
-MSG-PM-260: "Enter the version or the rate the exception is for" (RATE_EXCEPTION_INCOMPLETE)
-MSG-PM-261: "The validity date cannot be in the past" (RATE_EXCEPTION_VALIDITY_PAST)
-MSG-PM-262: "Package &lt;product code&gt; is priced on the current rate scheme: &lt;what&gt; needs an approved rate exception" (RATE_SCHEME_NOT_CURRENT)
-MSG-PM-263: "Rate exception &lt;reference&gt; does not approve &lt;what&gt; for &lt;product code&gt;" (RATE_SCHEME_NOT_CURRENT)
-MSG-PM-264: "Rate exception &lt;reference no&gt; is already decided" (RECORD_NOT_PENDING)</t>
+MSG-PM-259: "A rate exception is decided by someone other than its requester" (MAKER_CHECKER_VIOLATION)
+MSG-PM-260: "&lt;label&gt; not found: &lt;reference&gt;" (NOT_FOUND)
+MSG-PM-261: "Only package rate schemes need an exception" (PRODUCT_NOT_PACKAGED)
+MSG-PM-262: "Enter the version or the rate the exception is for" (RATE_EXCEPTION_INCOMPLETE)
+MSG-PM-263: "The validity date cannot be in the past" (RATE_EXCEPTION_VALIDITY_PAST)
+MSG-PM-264: "Package &lt;product code&gt; is priced on the current rate scheme: &lt;what&gt; needs an approved rate exception" (RATE_SCHEME_NOT_CURRENT)
+MSG-PM-265: "Rate exception &lt;reference&gt; does not approve &lt;what&gt; for &lt;product code&gt;" (RATE_SCHEME_NOT_CURRENT)
+MSG-PM-266: "Rate exception &lt;reference no&gt; is already decided" (RECORD_NOT_PENDING)</t>
         </is>
       </c>
       <c r="L271" s="12" t="inlineStr">
@@ -33380,7 +33382,7 @@
       <c r="K272" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-265: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
+MSG-PM-267: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)</t>
         </is>
       </c>
       <c r="L272" s="12" t="inlineStr">
@@ -33457,17 +33459,73 @@
       <c r="K273" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-267: "Enter an amount or rate of zero or more"
-MSG-PM-268: "Enter the effective-from date"
-MSG-PM-269: "The effective-to date is before the effective-from date"
-MSG-PM-271: "GL account &lt;code&gt; of the charge must be a postable account" (CHARGE_ACCOUNT_NOT_POSTABLE)
-MSG-PM-272: "Enter the amount or rate of the charge, zero or more" (CHARGE_VALUE_INVALID)
-MSG-PM-274: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
-MSG-PM-276: "A rate exception is decided by someone other than its requester" (MAKER_CHECKER_VIOLATION)
-MSG-PM-279: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
-MSG-PM-280: "Product &lt;code&gt; was not created by the migration" (PRODUCT_NOT_MIGRATED)
-MSG-PM-281: "Enter the reason for the rejection" (RATE_EXCEPTION_REASON_REQUIRED)
-MSG-PM-282: "Rate exception &lt;reference&gt; is already decided" (RECORD_NOT_PENDING)</t>
+MSG-PM-275: "Enter an amount or rate of zero or more"
+MSG-PM-276: "Enter at least &lt;min policies&gt; policies"
+MSG-PM-277: "Enter at least &lt;min premium&gt;"
+MSG-PM-278: "Enter the effective-from date"
+MSG-PM-279: "Enter the incentive amount or the incentive commission rate"
+MSG-PM-300: "The effective-to date is before the effective-from date"
+MSG-PM-301: "The incentive amount must be greater than zero"
+MSG-PM-302: "The incentive commission rate must be above 0% and at most 100%"
+MSG-PM-304: "GL account &lt;code&gt; of the charge must be a postable account" (CHARGE_ACCOUNT_NOT_POSTABLE)
+MSG-PM-305: "Enter the amount or rate of the charge, zero or more" (CHARGE_VALUE_INVALID)
+MSG-PM-306: "Select the company" (COMPANY_REQUIRED)
+MSG-PM-308: "The Period To date must be on or after the Period From date" (DATE_RANGE)
+MSG-PM-309: "The end date must be on or after the start date" (DATE_RANGE)
+MSG-PM-310: "&lt;label&gt; already exists: &lt;key&gt;" (DUPLICATE)
+MSG-PM-312: "A rate exception is decided by someone other than its requester" (MAKER_CHECKER_VIOLATION)
+MSG-PM-315: "&lt;label&gt; not found: &lt;id&gt;" (NOT_FOUND)
+MSG-PM-316: "Deactivation request not found: &lt;id&gt;" (NOT_FOUND)
+MSG-PM-317: "Placement Update Report not found: &lt;id&gt;" (NOT_FOUND)
+MSG-PM-318: "Product master change not found: &lt;id&gt;" (NOT_FOUND)
+MSG-PM-319: "Quotation request not found: &lt;id&gt;" (NOT_FOUND)
+MSG-PM-320: "Only the selected approver can decide this request" (PKG_DEACTIVATION_APPROVER)
+MSG-PM-321: "Select an approver who may approve package deactivation requests" (PKG_DEACTIVATION_APPROVER)
+MSG-PM-322: "Select another approver who may approve package deactivation requests" (PKG_DEACTIVATION_APPROVER)
+MSG-PM-323: "The deactivation effective date must be today or later" (PKG_DEACTIVATION_DATE)
+MSG-PM-324: "Deactivation request &lt;request no&gt; is already &lt;root&gt;" (PKG_DEACTIVATION_DECIDED)
+MSG-PM-325: "Only an active package can be deactivated" (PKG_DEACTIVATION_NOT_ACTIVE)
+MSG-PM-326: "Package &lt;product code&gt; already has the pending deactivation request &lt;request no&gt;" (PKG_DEACTIVATION_PENDING)
+MSG-PM-327: "Select the reason for deactivation" (PKG_DEACTIVATION_REASON)
+MSG-PM-328: "Enter the approval remarks of the rejection" (PKG_DEACTIVATION_REMARKS)
+MSG-PM-329: "Only the requestor can withdraw the request" (PKG_DEACTIVATION_REQUESTOR)
+MSG-PM-330: "Packages are deactivated through a retirement package request (setting PM_DEACTIVATION_ROUTE)" (PKG_DEACTIVATION_ROUTE)
+MSG-PM-331: "The deployment is requested once every required approval is complete" (PKG_DEPLOYMENT_NOT_READY)
+MSG-PM-332: "The incentive amount must be greater than zero" (PKG_INCENTIVE_AMOUNT)
+MSG-PM-333: "The incentive commission rate must be above 0% and at most 100%" (PKG_INCENTIVE_RATE)
+MSG-PM-334: "An incentive-eligible record needs the incentive amount or the incentive commission rate" (PKG_INCENTIVE_REQUIRED)
+MSG-PM-335: "Select one or more approvers of the ManCom approver list" (PKG_MANCOM_APPROVERS)
+MSG-PM-336: "No ManCom approval of this request waits for you" (PKG_MANCOM_NOT_YOURS)
+MSG-PM-337: "Enter the remarks of the rejection or the return" (PKG_MANCOM_REMARKS)
+MSG-PM-338: "ManCom approvers are selected once the request is for ManCom" (PKG_MANCOM_STAGE)
+MSG-PM-339: "This approval is given by the &lt;1&gt;" (PKG_MARKETING_LEVEL)
+MSG-PM-340: "The estimated number of policies to be issued must be at least &lt;policies&gt;" (PKG_MIN_POLICIES)
+MSG-PM-341: "The estimated total basic premium must be at least &lt;premium&gt;" (PKG_MIN_PREMIUM)
+MSG-PM-342: "Request not found" (PKG_NOT_FOUND)
+MSG-PM-343: "The source of a package request is Marketing, TSU or Insurer" (PKG_SOURCE)
+MSG-PM-344: "Select an approver, other than you, who may approve products" (PM_APPROVER)
+MSG-PM-345: "Enter the client's remarks for &lt;response&gt;" (PM_CLIENT_REMARKS)
+MSG-PM-346: "Choose Accepted, Rejected or Return for Revision" (PM_CLIENT_RESPONSE)
+MSG-PM-347: "The response date cannot be in the future" (PM_CLIENT_RESPONSE_DATE)
+MSG-PM-348: "The client responds once the proposal was sent" (PM_CLIENT_RESPONSE_STAGE)
+MSG-PM-349: "New packages are created through package requests" (PM_DIRECT_MAINTENANCE_OFF)
+MSG-PM-350: "Complete the Final Terms for Proposal first" (PM_FINAL_TERMS)
+MSG-PM-351: "Only a failed product master change is processed again" (PM_MASTER_NOT_FAILED)
+MSG-PM-352: "Select at least one insurer for the proposal" (PM_PROPOSAL_INSURER)
+MSG-PM-353: "Select the insurers and proceed to the proposal first" (PM_PROPOSAL_INSURER)
+MSG-PM-354: "&lt;insurer name&gt; has not given terms to propose" (PM_PROPOSAL_NO_TERMS)
+MSG-PM-355: "Insurers are selected while the insurers' terms come in" (PM_PROPOSAL_STAGE)
+MSG-PM-356: "Insurers are selected while the package terms are negotiated" (PM_PROPOSAL_STAGE)
+MSG-PM-357: "The proposal is generated once the terms are agreed" (PM_PROPOSAL_STAGE)
+MSG-PM-358: "The insurer response is Approved, Not Covered or Others" (PM_TERMS_ANSWER)
+MSG-PM-359: "Choose fields of the comparative table" (PM_TERMS_FIELD)
+MSG-PM-360: "&lt;code&gt; is not an insurer of this request" (PM_TERMS_INSURER)
+MSG-PM-361: "&lt;insurer code&gt; is not an insurer of this request" (PM_TERMS_INSURER)
+MSG-PM-362: "Specify the insurer's actual response for Others" (PM_TERMS_OTHER)
+MSG-PM-363: "A comparative table belongs to a quotation or package request" (PM_TERMS_RECORD)
+MSG-PM-364: "Product &lt;code&gt; was not created by the migration" (PRODUCT_NOT_MIGRATED)
+MSG-PM-365: "Enter the reason for the rejection" (RATE_EXCEPTION_REASON_REQUIRED)
+MSG-PM-366: "Rate exception &lt;reference&gt; is already decided" (RECORD_NOT_PENDING)</t>
         </is>
       </c>
       <c r="L273" s="12" t="inlineStr">
@@ -33544,13 +33602,13 @@
       <c r="K274" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-PM-270: "You are not permitted to perform this action" (ACCESS_DENIED)
-MSG-PM-273: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
-MSG-PM-275: "The system could not complete the request. Try again; if it continues, contact support with the reference." (INTERNAL_ERROR)
-MSG-PM-277: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
-MSG-PM-278: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
-MSG-PM-283: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
-MSG-PM-284: "Invalid request" (VALIDATION_FAILED)</t>
+MSG-PM-303: "You are not permitted to perform this action" (ACCESS_DENIED)
+MSG-PM-307: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
+MSG-PM-311: "The system could not complete the request. Try again; if it continues, contact support with the reference." (INTERNAL_ERROR)
+MSG-PM-313: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
+MSG-PM-314: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
+MSG-PM-367: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
+MSG-PM-368: "Invalid request" (VALIDATION_FAILED)</t>
         </is>
       </c>
       <c r="L274" s="12" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
@@ -3659,7 +3659,7 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>WT-A.15, WT-A.16, WT-A.17, WT-A.20, WT-B.10 ..., WT-B.9</t>
+          <t>WT-A.14, WT-A.15, WT-A.16, WT-A.17, WT-A.20, WT-B.10 ..., WT-B.9, WT-B.9 ...</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="H68" s="12" t="inlineStr">
         <is>
-          <t>WT-A.12, WT-A.3, WT-A.4, WT-A.5, WT-A.6, WT-B.1, WT-B.1 ..., WT-B.2, WT-B.3, WT-B.4 ...</t>
+          <t>WT-A.12, WT-A.14, WT-A.14 ..., WT-A.3, WT-A.4, WT-A.5, WT-A.6, WT-B.1, WT-B.2, WT-B.3 ...</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>WT-A.10, WT-A.13, WT-A.14 ..., WT-A.7, WT-A.8, WT-A.9, WT-B.5, WT-B.6</t>
+          <t>WT-A.10, WT-A.13, WT-A.7, WT-A.8, WT-A.9, WT-B.5, WT-B.5 ..., WT-B.6</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="H78" s="12" t="inlineStr">
         <is>
-          <t>WT-A.13, WT-A.14, WT-B.8</t>
+          <t>WT-A.13, WT-B.8</t>
         </is>
       </c>
     </row>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="H83" s="12" t="inlineStr">
         <is>
-          <t>WT-A.12, WT-A.3, WT-A.4, WT-A.5, WT-A.6, WT-B.1, WT-B.1 ..., WT-B.2</t>
+          <t>WT-A.12, WT-A.14 ..., WT-A.3, WT-A.4, WT-A.5, WT-A.6, WT-B.1, WT-B.2</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>WT-A.10, WT-A.13, WT-A.14 ..., WT-A.7, WT-A.8, WT-A.9</t>
+          <t>WT-A.10, WT-A.13, WT-A.7, WT-A.8, WT-A.9, WT-B.5 ...</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="H92" s="12" t="inlineStr">
         <is>
-          <t>WT-A.13, WT-A.14, WT-B.8</t>
+          <t>WT-A.13, WT-B.8</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="H98" s="12" t="inlineStr">
         <is>
-          <t>WT-A.13, WT-A.14, WT-B.8</t>
+          <t>WT-A.13, WT-B.8</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>WT-A.13, WT-A.14, WT-B.8</t>
+          <t>WT-A.13, WT-B.8</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="H107" s="12" t="inlineStr">
         <is>
-          <t>WT-A.12, WT-A.15, WT-A.16, WT-A.16 ..., WT-A.17, WT-A.20, WT-A.4, WT-A.5, WT-A.6, WT-B.10 ..., WT-B.9</t>
+          <t>WT-A.12, WT-A.14, WT-A.15, WT-A.15 ..., WT-A.16, WT-A.17, WT-A.20, WT-A.4, WT-A.5, WT-A.6, WT-B.9 ...</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="H108" s="12" t="inlineStr">
         <is>
-          <t>WT-A.15, WT-A.16, WT-A.17, WT-A.20, WT-B.10 ..., WT-B.9</t>
+          <t>WT-A.14, WT-A.15, WT-A.16, WT-A.17, WT-A.20, WT-B.10 ..., WT-B.9, WT-B.9 ...</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H110" s="12" t="inlineStr">
         <is>
-          <t>WT-A.12, WT-A.3, WT-A.4, WT-A.5, WT-A.6, WT-B.1 ...</t>
+          <t>WT-A.12, WT-A.14 ..., WT-A.3, WT-A.4, WT-A.5, WT-A.6</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="H129" s="12" t="inlineStr">
         <is>
-          <t>WT-A.13, WT-A.14, WT-B.8</t>
+          <t>WT-A.13, WT-B.8</t>
         </is>
       </c>
     </row>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="H149" s="12" t="inlineStr">
         <is>
-          <t>WT-A.12, WT-A.3, WT-A.4, WT-A.5, WT-A.6, WT-B.1 ...</t>
+          <t>WT-A.12, WT-A.14 ..., WT-A.3, WT-A.4, WT-A.5, WT-A.6</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="H155" s="12" t="inlineStr">
         <is>
-          <t>WT-A.10, WT-A.13, WT-A.14 ..., WT-A.7, WT-A.8, WT-A.9</t>
+          <t>WT-A.10, WT-A.13, WT-A.7, WT-A.8, WT-A.9, WT-B.5 ...</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="H156" s="12" t="inlineStr">
         <is>
-          <t>WT-A.13, WT-A.14, WT-B.8</t>
+          <t>WT-A.13, WT-B.8</t>
         </is>
       </c>
     </row>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="H158" s="12" t="inlineStr">
         <is>
-          <t>WT-A.13, WT-A.14, WT-B.8</t>
+          <t>WT-A.13, WT-B.8</t>
         </is>
       </c>
     </row>
@@ -31505,7 +31505,7 @@
 MSG-PM-049: "Rates and amounts cannot be negative" (PKG_AMOUNT_NEGATIVE)
 MSG-PM-050: "The insurer chosen did not offer terms in this round" (PKG_INSURER_NOT_OFFERED)
 MSG-PM-051: "Unknown role &lt;given&gt;" (PKG_INSURER_ROLE_INVALID)
-MSG-PM-052: "Enter the rate offered by &lt;insurer name&gt; (&lt;outcome&gt;)" (PKG_RESPONSE_RATE_REQUIRED)
+MSG-PM-052: "Enter the rate offered by &lt;insurer name&gt; (&lt;&gt;)" (PKG_RESPONSE_RATE_REQUIRED)
 MSG-PM-053: "Round &lt;round no&gt; is closed: key in the latest round" (PKG_ROUND_CLOSED)
 MSG-PM-054: "Marketing reviews the terms of a client-specific package" (PKG_SCOPE_CLIENT)
 MSG-PM-055: "A generic programme goes straight to the requirements" (PKG_SCOPE_GENERIC)

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
@@ -21932,7 +21932,7 @@
       <c r="H161" s="12" t="inlineStr">
         <is>
           <t>1. Upload the signed package slip.
-2. Edit the advisory - groups Marketing and Operations, e-mail operations@brokerverse-seed.ph, subject "MTR15 renewed", text; save.
+2. Edit the advisory - groups Marketing and Operations, e-mail operations@uat.brokerverse.cloud, subject "MTR15 renewed", text; save.
 3. Click Send. As ao open the notification bell.</t>
         </is>
       </c>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
@@ -14,10 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test cases" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answered in the BDOI FRS" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UAT entry and exit criteria" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change requests" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$50</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$C$42</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
@@ -29,7 +30,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Answered in the BDOI FRS'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'UAT entry and exit criteria'!$A$4:$B$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'UAT entry and exit criteria'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Lists'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change requests'!$A$4:$F$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Change requests'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Lists'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -405,7 +408,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="971550" cy="285750"/>
@@ -718,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E33"/>
+  <dimension ref="B4:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -752,7 +755,7 @@
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>BRD-03 Product Maintenance – FRS v1.2 in BDOI's template</t>
+          <t>BRD-03 Product Maintenance – FRS v1.3 in BDOI's template</t>
         </is>
       </c>
     </row>
@@ -910,7 +913,7 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>The test cases of the FRS v1.2 with their execution columns</t>
+          <t>The test cases of the FRS v1.3 with their execution columns</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
@@ -947,25 +950,32 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="9" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Change requests</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>The change requests of the FRS v1.3 linked to their FRS items and test cases</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="15" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>Passed</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>Failed</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr"/>
@@ -973,13 +983,21 @@
     <row r="30">
       <c r="B30" s="17" t="inlineStr">
         <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="17" t="inlineStr">
+        <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr"/>
-    </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="B33" s="18" t="inlineStr">
+      <c r="C31" s="16" t="inlineStr"/>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="B34" s="18" t="inlineStr">
         <is>
           <t>Prepared by iorta TechNXT for BDOI. Confidential – BDOI.</t>
         </is>
@@ -993,6 +1011,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId7"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -1005,7 +1024,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
 </worksheet>
 </file>
 
@@ -1015,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1163,7 +1182,7 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>FRPM sub-item of the FRS v1.2</t>
+          <t>FRPM sub-item of the FRS v1.3</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr"/>
@@ -1800,8 +1819,116 @@
       </c>
       <c r="D44" s="14" t="inlineStr"/>
     </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Change requests</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>CR No.</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>Change request (FRS Annex Y.2, CR register, CR effort workbook)</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>Change requests</t>
+        </is>
+      </c>
+      <c r="B46" s="21" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>The change</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Change requests</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>BRD reference</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>BRD ID it extends</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>Change requests</t>
+        </is>
+      </c>
+      <c r="B48" s="21" t="inlineStr">
+        <is>
+          <t>FRS reference</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>FRPM item or annex row</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>Change requests</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>Test cases affected</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Test cases of this workbook to update</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>Change requests</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="inlineStr">
+        <is>
+          <t>Effort (md)</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>Man-days (CR effort workbook)</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:D44"/>
+  <autoFilter ref="A4:D50"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -8959,7 +9086,7 @@
     <row r="2">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>The test cases of the FRS v1.2 with their execution columns</t>
+          <t>The test cases of the FRS v1.3 with their execution columns</t>
         </is>
       </c>
     </row>
@@ -50750,7 +50877,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>The FRS v1.2 and this workbook are signed off; open decisions affecting the tested steps are decided (FRS Annex V, Annex M).</t>
+          <t>The FRS v1.3 and this workbook are signed off; open decisions affecting the tested steps are decided (FRS Annex V, Annex M).</t>
         </is>
       </c>
     </row>
@@ -50885,6 +51012,251 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Change requests</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>The change requests of the FRS v1.3 linked to their FRS items and test cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="23" t="n"/>
+      <c r="B3" s="23" t="n"/>
+      <c r="C3" s="23" t="n"/>
+      <c r="D3" s="23" t="n"/>
+      <c r="E3" s="23" t="n"/>
+      <c r="F3" s="23" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>CR No.</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>BRD reference</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>FRS reference</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>Test cases affected</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>Effort (md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>CR-PM-101</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Quotation Slip decision notice to the preparer</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.012 (extends)</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>FRPM.006.01, FRPM.012.01; Annex P NT-16</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>TC-PM-013.1-01, TC-PM-013.2-01, TC-PM-013.3-01, TC-PM-030.1-01, TC-PM-030.2-01, TC-PM-030.3-01, TC-PM-030.3-02, TC-PM-030.4-01, TC-PM-030.4-02, TC-PM-030.5-01, TC-PM-SCR-05, TC-PM-MSG-04, TC-NB-053.1-01, TC-NB-053.2-01, TC-NB-053.3-01, TC-NB-053.3-02, TC-NB-053.3-03, TC-FRPM.006.01-AC1, TC-FRPM.006.01-AC2, TC-FRPM.006.01-AC3, TC-FRPM.012.01-AC1, TC-FRPM.012.01-AC2, TC-FRPM.012.01-AC3, TC-FRPM.012.01-AC4</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>CR-PM-102</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>ManCom e-mails in BDOI's wording, with the President's text</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.015 (extends)</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>FRPM.014.01; Annex P NT-13, NT-14</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>TC-PM-041.5-01, TC-PM-041.5-02, TC-PM-041.1-01, TC-PM-041.1-02, TC-PM-041.2-01, TC-PM-041.3-01, TC-PM-041.4-01, TC-PM-041.4-02, TC-FRPM.014.01-AC1, TC-FRPM.014.01-AC2, TC-FRPM.014.01-AC3</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>CR-PM-103</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Old and new field values of product master changes in the audit log</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.024 (extends)</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>FRPM.021.01, FRPM.021.02; Annex M.5</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>TC-PM-005.4-01, TC-PM-005.1-01, TC-PM-005.2-01, TC-PM-005.3-01, TC-PM-SCR-27, TC-FRPM.021.01-AC1, TC-FRPM.021.01-AC2, TC-FRPM.021.02-AC1</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>CR-PM-104</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Accessibility of the Product Maintenance screens (WCAG 2.2 level AA)</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Annex T, T-15</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>To be written if the change is approved</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>CR-PM-105</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>'Due soon' marker at 80% of the stage service level</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.021 (extends)</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>FRPM.001.01</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>TC-PM-070.1-01, TC-PM-070.1-02, TC-PM-070.2-01, TC-PM-070.3-01, TC-PM-070.3-02, TC-PM-070.4-01, TC-PM-070.4-02, TC-PM-073.1-01, TC-PM-073.1-02, TC-PM-073.2-01, TC-PM-073.3-01, TC-PM-073.2-02, TC-PM-SCR-01, TC-PM-SCR-23, TC-FRPM.001.01-AC1, TC-FRPM.001.01-AC2, TC-FRPM.001.01-AC3</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:F9"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:F509">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
@@ -30,7 +30,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Answered in the BDOI FRS'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'UAT entry and exit criteria'!$A$4:$B$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'UAT entry and exit criteria'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change requests'!$A$4:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change requests'!$A$4:$F$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Change requests'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Lists'!$1:$1</definedName>
   </definedNames>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -51012,7 +51012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -51145,26 +51145,26 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Old and new field values of product master changes in the audit log</t>
+          <t>Accessibility of the Product Maintenance screens (WCAG 2.2 level AA)</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>BRPM.024 (extends)</t>
+          <t>Not in BRD</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>FRPM.021.01, FRPM.021.02; Annex M.5</t>
+          <t>Annex T, T-15</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-005.4-01, TC-PM-005.1-01, TC-PM-005.2-01, TC-PM-005.3-01, TC-PM-SCR-27, TC-FRPM.021.01-AC1, TC-FRPM.021.01-AC2, TC-FRPM.021.02-AC1</t>
+          <t>To be written if the change is approved</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="8">
@@ -51175,64 +51175,34 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Accessibility of the Product Maintenance screens (WCAG 2.2 level AA)</t>
+          <t>'Due soon' marker at 80% of the stage service level</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Not in BRD</t>
+          <t>BRPM.021 (extends)</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Annex T, T-15</t>
+          <t>FRPM.001.01</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>To be written if the change is approved</t>
+          <t>TC-PM-070.1-01, TC-PM-070.1-02, TC-PM-070.2-01, TC-PM-070.3-01, TC-PM-070.3-02, TC-PM-070.4-01, TC-PM-070.4-02, TC-PM-073.1-01, TC-PM-073.1-02, TC-PM-073.2-01, TC-PM-073.3-01, TC-PM-073.2-02, TC-PM-SCR-01, TC-PM-SCR-23, TC-FRPM.001.01-AC1, TC-FRPM.001.01-AC2, TC-FRPM.001.01-AC3</t>
         </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>CR-PM-105</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>'Due soon' marker at 80% of the stage service level</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>BRPM.021 (extends)</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>FRPM.001.01</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>TC-PM-070.1-01, TC-PM-070.1-02, TC-PM-070.2-01, TC-PM-070.3-01, TC-PM-070.3-02, TC-PM-070.4-01, TC-PM-070.4-02, TC-PM-073.1-01, TC-PM-073.1-02, TC-PM-073.2-01, TC-PM-073.3-01, TC-PM-073.2-02, TC-PM-SCR-01, TC-PM-SCR-23, TC-FRPM.001.01-AC1, TC-FRPM.001.01-AC2, TC-FRPM.001.01-AC3</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="n">
         <v>3.5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F9"/>
+  <autoFilter ref="A4:F8"/>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:F509">
+  <conditionalFormatting sqref="A5:F508">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
@@ -30,7 +30,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Answered in the BDOI FRS'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'UAT entry and exit criteria'!$A$4:$B$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'UAT entry and exit criteria'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change requests'!$A$4:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change requests'!$A$4:$F$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Change requests'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Lists'!$1:$1</definedName>
   </definedNames>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -51012,7 +51012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -51085,124 +51085,34 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Quotation Slip decision notice to the preparer</t>
+          <t>Accessibility of the Product Maintenance screens (WCAG 2.2 level AA)</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>BRPM.012 (extends)</t>
+          <t>Not in BRD</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>FRPM.006.01, FRPM.012.01; Annex P NT-16</t>
+          <t>Annex T, T-15</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>TC-PM-013.1-01, TC-PM-013.2-01, TC-PM-013.3-01, TC-PM-030.1-01, TC-PM-030.2-01, TC-PM-030.3-01, TC-PM-030.3-02, TC-PM-030.4-01, TC-PM-030.4-02, TC-PM-030.5-01, TC-PM-SCR-05, TC-PM-MSG-04, TC-NB-053.1-01, TC-NB-053.2-01, TC-NB-053.3-01, TC-NB-053.3-02, TC-NB-053.3-03, TC-FRPM.006.01-AC1, TC-FRPM.006.01-AC2, TC-FRPM.006.01-AC3, TC-FRPM.012.01-AC1, TC-FRPM.012.01-AC2, TC-FRPM.012.01-AC3, TC-FRPM.012.01-AC4</t>
+          <t>To be written if the change is approved</t>
         </is>
       </c>
       <c r="F5" s="12" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>CR-PM-102</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>ManCom e-mails in BDOI's wording, with the President's text</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>BRPM.015 (extends)</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>FRPM.014.01; Annex P NT-13, NT-14</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>TC-PM-041.5-01, TC-PM-041.5-02, TC-PM-041.1-01, TC-PM-041.1-02, TC-PM-041.2-01, TC-PM-041.3-01, TC-PM-041.4-01, TC-PM-041.4-02, TC-FRPM.014.01-AC1, TC-FRPM.014.01-AC2, TC-FRPM.014.01-AC3</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>CR-PM-103</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Accessibility of the Product Maintenance screens (WCAG 2.2 level AA)</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Annex T, T-15</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>To be written if the change is approved</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="n">
         <v>11.5</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>CR-PM-104</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>'Due soon' marker at 80% of the stage service level</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>BRPM.021 (extends)</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>FRPM.001.01</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>TC-PM-070.1-01, TC-PM-070.1-02, TC-PM-070.2-01, TC-PM-070.3-01, TC-PM-070.3-02, TC-PM-070.4-01, TC-PM-070.4-02, TC-PM-073.1-01, TC-PM-073.1-02, TC-PM-073.2-01, TC-PM-073.3-01, TC-PM-073.2-02, TC-PM-SCR-01, TC-PM-SCR-23, TC-FRPM.001.01-AC1, TC-FRPM.001.01-AC2, TC-FRPM.001.01-AC3</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:F8"/>
+  <autoFilter ref="A4:F5"/>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:F508">
+  <conditionalFormatting sqref="A5:F505">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -731,13 +731,16 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1"/>
+    <row r="3"/>
     <row r="4" ht="6" customHeight="1">
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
       <c r="D4" s="1" t="n"/>
       <c r="E4" s="1" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -766,6 +769,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -838,6 +842,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -965,6 +970,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="B28" s="9" t="inlineStr">
         <is>
@@ -996,6 +1002,8 @@
       </c>
       <c r="C31" s="16" t="inlineStr"/>
     </row>
+    <row r="32"/>
+    <row r="33"/>
     <row r="34" ht="26" customHeight="1">
       <c r="B34" s="18" t="inlineStr">
         <is>
@@ -1057,6 +1065,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -9488,7 +9497,7 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Administration &gt; System Parameters shows LOGIN_MAX_FAILED_ATTEMPTS (3 as delivered).
+          <t>Administration &gt; System Parameters shows LOGIN_MAX_FAILED_ATTEMPTS (3 by default).
 Data: TD-PM-01 SIT/UAT users and roles</t>
         </is>
       </c>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
@@ -43,7 +43,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -140,6 +140,11 @@
       <color rgb="00C62828"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -210,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -267,6 +272,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1025,7 +1031,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1942,7 +1948,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2588,7 +2594,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -9045,7 +9051,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -27066,7 +27072,7 @@
       </c>
       <c r="J222" s="12" t="inlineStr">
         <is>
-          <t>One change with product, version and effective date is listed on Product Master Transfers and sent in the file ProductMaster_&lt;yyyyMMddHHmmss&gt;.csv (to the receiving system simulator in SIT and UAT).</t>
+          <t>One change with product, version and effective date is listed on Product Master Transfers and sent in the file ProductMaster_&lt;yyyyMMddHHmmss&gt;.csv (in SIT and UAT, to the test account of BDOI's receiving system provided under the Integration scope).</t>
         </is>
       </c>
       <c r="K222" s="12" t="inlineStr">
@@ -27147,7 +27153,7 @@
       </c>
       <c r="J223" s="12" t="inlineStr">
         <is>
-          <t>The change is Sent with its file and time; the simulator inbox shows the file with its records.</t>
+          <t>The change is Sent with its file and time; the test account of BDOI's receiving system (Integration scope) shows the file with its records.</t>
         </is>
       </c>
       <c r="K223" s="12" t="inlineStr">
@@ -48485,7 +48491,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -50825,7 +50831,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -51005,7 +51011,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -51130,7 +51136,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -51184,85 +51190,85 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="28" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="28" t="inlineStr">
         <is>
           <t>Answered</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="28" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>Partly answered</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>Exit</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>Answered earlier</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>Not applicable</t>
         </is>
@@ -51273,7 +51279,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
@@ -48489,7 +48489,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Cases and Traceability&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
@@ -50904,7 +50904,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>The BIBS UAT environment is available with the SIT/UAT data and the users of the walkthrough users workbook; passwords issued by the iorta TechNXT Project Team.</t>
+          <t>The UAT environment is available with the test data of the test plan and the persona users of the walkthrough users workbook; passwords issued by the iorta TechNXT Project Team.</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_RTM_BRD-03_Test_Cases_and_Traceability_v1.0.xlsx
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>Sign-in ID</t>
+          <t>User (FRS Annex K)</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>UAT sign-in ID (walkthrough users workbook)</t>
+          <t>Fictitious user of the persona (FRS Annex K)</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr"/>
@@ -9075,7 +9075,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>Sign-in ID</t>
+          <t>User (FRS Annex K)</t>
         </is>
       </c>
       <c r="G4" s="24" t="inlineStr">
@@ -9251,18 +9251,18 @@
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
+          <t>Data: TD-PM-01 users and roles of the test data prepared for the walkthrough</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
           <t>1. Open the BIBS URL.
-2. Enter user ID ao and The SIT/UAT password; click Sign in.
+2. Enter the user ID and password of Aileen Torres (Marketing AO); click Sign in.
 3. Open the side menu.</t>
         </is>
       </c>
@@ -9334,17 +9334,17 @@
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
+          <t>Data: TD-PM-01 users and roles of the test data prepared for the walkthrough</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as tsuhead.
+          <t>1. Log in as Tomas Vergara (TSU Head).
 2. Open the side menu, section Product Maintenance.</t>
         </is>
       </c>
@@ -9416,17 +9416,17 @@
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
+          <t>Data: TD-PM-01 users and roles of the test data prepared for the walkthrough</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>1. Enter user ID ao and a wrong password; click Sign in.</t>
+          <t>1. Enter the user ID of Aileen Torres (Marketing AO) and a wrong password; click Sign in.</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
@@ -9498,18 +9498,18 @@
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
           <t>Administration &gt; System Parameters shows LOGIN_MAX_FAILED_ATTEMPTS (3 by default).
-Data: TD-PM-01 SIT/UAT users and roles</t>
+Data: TD-PM-01 users and roles of the test data prepared for the walkthrough</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>1. Enter user ID ao2 with a wrong password as many times as the threshold.
+          <t>1. Enter the user ID of another Marketing AO with a wrong password as many times as the threshold.
 2. Enter the correct password.</t>
         </is>
       </c>
@@ -9582,17 +9582,17 @@
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
+          <t>Data: TD-PM-01 users and roles of the test data prepared for the walkthrough</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>1. Enter user ID ao2 with a wrong password (threshold minus 1) times.
+          <t>1. Enter the user ID of another Marketing AO with a wrong password (threshold minus 1) times.
 2. Enter the correct password.</t>
         </is>
       </c>
@@ -9664,19 +9664,19 @@
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Auditor</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
           <t>Cases TC-PM-001.1-01 and TC-PM-001.2-01 ran today.
-Data: TD-PM-01 SIT/UAT users and roles</t>
+Data: TD-PM-01 users and roles of the test data prepared for the walkthrough</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as auditor and open Administration &gt; Audit Trail.
-2. Filter on today's date and the users ao and ao2.</t>
+          <t>1. Log in as the Auditor and open Administration &gt; Audit Trail.
+2. Filter on today's date and two Marketing AO users.</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
@@ -9747,18 +9747,18 @@
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>Single sign-on through EIAM switched on in the test environment (User Access Maintenance FRS); the EIAM test account of tsu.
-Data: TD-PM-01 SIT/UAT users and roles</t>
+          <t>Single sign-on through EIAM switched on in the test environment (User Access Maintenance FRS); the EIAM test account of Teodoro Valdez (TSU Officer).
+Data: TD-PM-01 users and roles of the test data prepared for the walkthrough</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>1. Open BIBS and click Sign in with the BDO identity provider; sign in at EIAM with the test account of tsu.
+          <t>1. Open BIBS and click Sign in with the BDO identity provider; sign in at EIAM with the test account of Teodoro Valdez (TSU Officer).
 2. Open the side menu.</t>
         </is>
       </c>
@@ -9830,17 +9830,17 @@
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
+          <t>Data: TD-PM-01 users and roles of the test data prepared for the walkthrough</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as ao and open the side menu.</t>
+          <t>1. Log in as Aileen Torres (Marketing AO) and open the side menu.</t>
         </is>
       </c>
       <c r="I12" s="12" t="inlineStr">
@@ -9911,17 +9911,17 @@
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
+          <t>Data: TD-PM-01 users and roles of the test data prepared for the walkthrough</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as ao.
+          <t>1. Log in as Aileen Torres (Marketing AO).
 2. Open the address of the Validation Queue directly in the browser.</t>
         </is>
       </c>
@@ -9993,19 +9993,19 @@
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
+          <t>Data: TD-PM-01 users and roles of the test data prepared for the walkthrough</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Send a direct request to approve a request in FOR_MKT_APPROVAL.
-3. Log in as auditor and open Administration &gt; Audit Trail.</t>
+3. Log in as the Auditor and open Administration &gt; Audit Trail.</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
@@ -10077,18 +10077,18 @@
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>mkttl</t>
+          <t>Marites Hernandez</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>mkttl creates and submits a request (TD-PM-12).
+          <t>Marites Hernandez (Marketing TL / TH / UH) creates and submits a request (TD-PM-12).
 Data: TD-PM-12 New CGL request keyed in the test</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as mkttl and open the request.
+          <t>1. Log in as Marites Hernandez (Marketing TL / TH / UH) and open the request.
 2. Click Approve and send to TSU.</t>
         </is>
       </c>
@@ -10161,17 +10161,17 @@
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Garcia</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
+          <t>Data: TD-PM-01 users and roles of the test data prepared for the walkthrough</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as badmin and open Broking Setup &gt; User Access Matrix.
+          <t>1. Log in as Bea Garcia (Business Administrator) and open Broking Setup &gt; User Access Matrix.
 2. Choose the view By Action and the area PACKAGE_REQUEST.
 3. Switch to the view By Permission.
 4. Click Export to Excel in each view.</t>
@@ -10245,17 +10245,17 @@
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
+          <t>Data: TD-PM-01 users and roles of the test data prepared for the walkthrough</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as ao and open the address of the User Access Matrix directly in the browser.</t>
+          <t>1. Log in as Aileen Torres (Marketing AO) and open the address of the User Access Matrix directly in the browser.</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
@@ -10326,21 +10326,21 @@
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Garcia</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
+          <t>Data: TD-PM-01 users and roles of the test data prepared for the walkthrough</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as badmin; open Broking Setup &gt; Access Requests; click New Request.
+          <t>1. Log in as Bea Garcia (Business Administrator); open Broking Setup &gt; Access Requests; click New Request.
 2. Choose type Modify role permissions, role MKT_AO, permission to add PKG_REPORT_VIEW, justification "AO needs package reports".
-3. Submit. Log in as ao and check the Reports list.
-4. Log in as approver; open the request and click Approve.
-5. Log in as ao again and open Reports.</t>
+3. Submit. Log in as Aileen Torres (Marketing AO) and check the Reports list.
+4. Log in as Andres Bautista (New Business approver); open the request and click Approve.
+5. Log in as Aileen Torres (Marketing AO) again and open Reports.</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>Before approval ao has no package reports. After approval the role holds PKG_REPORT_VIEW and ao sees the Package Status Update Report.</t>
+          <t>Before approval Aileen Torres (Marketing AO) has no package reports. After approval the role holds PKG_REPORT_VIEW and Aileen Torres (Marketing AO) sees the Package Status Update Report.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
@@ -10411,13 +10411,13 @@
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Garcia</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
           <t>A test user holding ACCESS_REQUEST and ACCESS_APPROVE (set up by the test lead for this case) submitted a Modify role permissions request.
-Data: TD-PM-01 SIT/UAT users and roles</t>
+Data: TD-PM-01 users and roles of the test data prepared for the walkthrough</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -10494,12 +10494,12 @@
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Garcia</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
+          <t>Data: TD-PM-01 users and roles of the test data prepared for the walkthrough</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Garcia</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-PM-01 SIT/UAT users and roles</t>
+          <t>Data: TD-PM-01 users and roles of the test data prepared for the walkthrough</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -10658,18 +10658,18 @@
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>approver</t>
+          <t>Andres Bautista</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>badmin submitted a request to remove PRODUCT_VIEW from AUDITOR.
-Data: TD-PM-01 SIT/UAT users and roles</t>
+          <t>Bea Garcia (Business Administrator) submitted a request to remove PRODUCT_VIEW from AUDITOR.
+Data: TD-PM-01 users and roles of the test data prepared for the walkthrough</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as approver; open the request; click Reject and enter the reason "Auditor keeps read access".
+          <t>1. Log in as Andres Bautista (New Business approver); open the request; click Reject and enter the reason "Auditor keeps read access".
 2. Open Broking Setup &gt; User Access Matrix for AUDITOR.</t>
         </is>
       </c>
@@ -10680,7 +10680,7 @@
       </c>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>The request shows Rejected with the reason; AUDITOR still holds PRODUCT_VIEW; badmin is notified of the decision.</t>
+          <t>The request shows Rejected with the reason; AUDITOR still holds PRODUCT_VIEW; Bea Garcia (Business Administrator) is notified of the decision.</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
@@ -10741,13 +10741,13 @@
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Auditor</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
           <t>TC-PM-003.1-01 is done.
-Data: TD-PM-01 SIT/UAT users and roles</t>
+Data: TD-PM-01 users and roles of the test data prepared for the walkthrough</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>The request shows requester badmin, approver approver, dates and the permissions added; the audit trail holds the request, the decision and the applied change with users and times.</t>
+          <t>The request shows requester Bea Garcia (Business Administrator), approver Andres Bautista (New Business approver), dates and the permissions added; the audit trail holds the request, the decision and the applied change with users and times.</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
@@ -10823,12 +10823,12 @@
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>A round of TD-PM-12 is approved by tsulead and sent (TC-PM-030.2-01).
+          <t>A round of TD-PM-12 is approved by Teresa Villareal (TSU Team Lead) and sent (TC-PM-030.2-01).
 Data: TD-PM-04 Client-specific request in negotiation; TD-PM-11 Catalogue and insurer panel</t>
         </is>
       </c>
@@ -10906,7 +10906,7 @@
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
@@ -11070,12 +11070,12 @@
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>A user holding only a non-broking role (for example a GL user of the finance seed) exists.
+          <t>A user holding only a non-broking role (for example a GL user of the test data prepared for the walkthrough) exists.
 Data: TD-PM-04 Client-specific request in negotiation; TD-PM-11 Catalogue and insurer panel</t>
         </is>
       </c>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Auditor</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
@@ -11409,7 +11409,7 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as admin; open Administration &gt; Audit Trail and look for edit or delete actions on a row.
+          <t>1. Log in as the System Administrator; open Administration &gt; Audit Trail and look for edit or delete actions on a row.
 2. Ask the infrastructure administrator of the test environment to try to change, delete and clear audit entries directly.</t>
         </is>
       </c>
@@ -11461,7 +11461,7 @@
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>New Motor coverage is pending until badmin authorises it</t>
+          <t>New Motor coverage is pending until Bea Garcia (Business Administrator) authorises it</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
@@ -11491,11 +11491,11 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as mbs; open Coverages &amp; Clauses; click New Coverage.
+          <t>1. Log in as Monica Vergara (Marketing Business Services); open Coverages &amp; Clauses; click New Coverage.
 2. Line MOTOR, code UAT_ROADSIDE, name "Roadside assistance (UAT)", kind Extension; save.
 3. Open the draft version MTR12 v2 and look for the coverage in the coverage list.
-4. Log in as badmin; open My Approvals; authorise the coverage.
-5. As mbs, open MTR12 v2 again.</t>
+4. Log in as Bea Garcia (Business Administrator); open My Approvals; authorise the coverage.
+5. As Monica Vergara (Marketing Business Services), open MTR12 v2 again.</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>1. As mbs, open My Approvals and try to authorise UAT_ROADSIDE (before badmin does).</t>
+          <t>1. As Monica Vergara (Marketing Business Services), open My Approvals and try to authorise UAT_ROADSIDE (before Bea Garcia (Business Administrator) does).</t>
         </is>
       </c>
       <c r="I37" s="12" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Garcia</t>
         </is>
       </c>
       <c r="G38" s="12" t="inlineStr">
@@ -11986,9 +11986,9 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>1. Create coverage UAT_REJECT as mbs.
-2. As badmin, reject it with reason "Wrong line".
-3. As mbs, open the coverage.</t>
+          <t>1. Create coverage UAT_REJECT as Monica Vergara (Marketing Business Services).
+2. As Bea Garcia (Business Administrator), reject it with reason "Wrong line".
+3. As Monica Vergara (Marketing Business Services), open the coverage.</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>The coverage shows Rejected with the reason and is not offered on package versions; mbs can edit and resubmit it.</t>
+          <t>The coverage shows Rejected with the reason and is not offered on package versions; Monica Vergara (Marketing Business Services) can edit and resubmit it.</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
@@ -12071,7 +12071,7 @@
         <is>
           <t>1. Coverages &amp; Clauses &gt; Clauses &gt; New Clause; code UAT_W01, kind Warranty, line MOTOR, title "Garage warranty", effective from today, wording "Warranted that the vehicle is garaged overnight."; save.
 2. Open MTR12 v2, Insurer Terms of INS-MGIC, coverage OD_THEFT, Clauses list.
-3. As badmin, authorise UAT_W01 in My Approvals; reopen the Clauses list as mbs.</t>
+3. As Bea Garcia (Business Administrator), authorise UAT_W01 in My Approvals; reopen the Clauses list as Monica Vergara (Marketing Business Services).</t>
         </is>
       </c>
       <c r="I39" s="12" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G42" s="12" t="inlineStr">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
@@ -12470,18 +12470,18 @@
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>MBS added and badmin authorised a Line-scope rule on MOTOR, target Item, field Plate number, check Presence.
+          <t>MBS added and Bea Garcia (Business Administrator) authorised a Line-scope rule on MOTOR, target Item, field Plate number, check Presence.
 Data: TD-PM-11 Catalogue and insurer panel; TD-PM-14 Masked quotation data</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as ao; create a quotation on MTR12 with one vehicle without plate number; submit.</t>
+          <t>1. Log in as Aileen Torres (Marketing AO); create a quotation on MTR12 with one vehicle without plate number; submit.</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G45" s="12" t="inlineStr">
@@ -12565,7 +12565,7 @@
         <is>
           <t>1. Open product MTR12, Field Rules &amp; Documents tab; click New Rule.
 2. Scope Line, line MOTOR, target Item, field Plate number, check type Presence; save.
-3. As badmin, authorise the rule.</t>
+3. As Bea Garcia (Business Administrator), authorise the rule.</t>
         </is>
       </c>
       <c r="I45" s="12" t="inlineStr">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G46" s="12" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G48" s="12" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G50" s="12" t="inlineStr">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="G51" s="12" t="inlineStr">
@@ -13058,8 +13058,8 @@
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>1. As admin, open Broking Setup &gt; Document Templates, template PKG_QUOTATION_SLIP; note the current version.
-2. As tsu, open the Documents tab of PKR-2026-900003 and the QS record.</t>
+          <t>1. As the System Administrator, open Broking Setup &gt; Document Templates, template PKG_QUOTATION_SLIP; note the current version.
+2. As Teodoro Valdez (TSU Officer), open the Documents tab of PKR-2026-900003 and the QS record.</t>
         </is>
       </c>
       <c r="I51" s="12" t="inlineStr">
@@ -13130,18 +13130,18 @@
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>In the test environment only, admin end-dates template PKG_SLIP.
+          <t>In the test environment only, the System Administrator end-dates template PKG_SLIP.
 Data: TD-PM-04 Client-specific request in negotiation; TD-PM-05 UPDATE request at ManCom</t>
         </is>
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>1. As tsu, download the package slip of PKR-2026-900004.
+          <t>1. As Teodoro Valdez (TSU Officer), download the package slip of PKR-2026-900004.
 2. Restore the template afterwards.</t>
         </is>
       </c>
@@ -13214,7 +13214,7 @@
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G53" s="12" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G54" s="12" t="inlineStr">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G55" s="12" t="inlineStr">
@@ -13460,7 +13460,7 @@
       </c>
       <c r="F56" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G56" s="12" t="inlineStr">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="H56" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as ao; New Quotation on MTR10; choose insurer INS-MPI (not on the panel); rate the quotation.</t>
+          <t>1. Log in as Aileen Torres (Marketing AO); New Quotation on MTR10; choose insurer INS-MPI (not on the panel); rate the quotation.</t>
         </is>
       </c>
       <c r="I56" s="12" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G58" s="12" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as ao; Package Requests; click New Package Request.
+          <t>1. Log in as Aileen Torres (Marketing AO); Package Requests; click New Package Request.
 2. Type New package, scope Generic programme, name "UAT CGL Programme", line LIABILITY, cover type CGL, reason New programme for a market segment.
 3. Requested terms - add coverage CGL_BI (included), package end 31-Dec-2027, target insurers INS-MGIC and INS-LAC; attach the request form.
 4. Click Save; note the number; click Submit for approval.</t>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>On save the request gets a number PKR-2026-nnnnnn and stage DRAFT. On submission it moves to FOR_MKT_APPROVAL, the milestone Submitted shows ao and the time, and mkttl receives a notification.</t>
+          <t>On save the request gets a number PKR-2026-nnnnnn and stage DRAFT. On submission it moves to FOR_MKT_APPROVAL, the milestone Submitted shows Aileen Torres (Marketing AO) and the time, and Marites Hernandez (Marketing TL / TH / UH) receives a notification.</t>
         </is>
       </c>
       <c r="K58" s="12" t="inlineStr">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G59" s="12" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G60" s="12" t="inlineStr">
@@ -13872,7 +13872,7 @@
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G62" s="12" t="inlineStr">
@@ -14036,7 +14036,7 @@
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G63" s="12" t="inlineStr">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G64" s="12" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G65" s="12" t="inlineStr">
@@ -14282,7 +14282,7 @@
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G66" s="12" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G67" s="12" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="F68" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G68" s="12" t="inlineStr">
@@ -14456,7 +14456,7 @@
       </c>
       <c r="H68" s="12" t="inlineStr">
         <is>
-          <t>1. Open PKR-2026-900001 as ao; click Void; select reason Duplicate record; confirm.</t>
+          <t>1. Open PKR-2026-900001 as Aileen Torres (Marketing AO); click Void; select reason Duplicate record; confirm.</t>
         </is>
       </c>
       <c r="I68" s="12" t="inlineStr">
@@ -14527,19 +14527,19 @@
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>ao submitted the request of TC-PM-020.1-01.
+          <t>Aileen Torres (Marketing AO) submitted the request of TC-PM-020.1-01.
 Data: TD-PM-12 New CGL request keyed in the test</t>
         </is>
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>1. As ao, open the request.
-2. Send a direct request to approve the request, signed in as ao.</t>
+          <t>1. As Aileen Torres (Marketing AO), open the request.
+2. Send a direct request to approve the request, signed in as Aileen Torres (Marketing AO).</t>
         </is>
       </c>
       <c r="I69" s="12" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="J69" s="12" t="inlineStr">
         <is>
-          <t>No approve button is shown to ao; the direct request is refused and the request stays in FOR_MKT_APPROVAL.</t>
+          <t>No approve button is shown to Aileen Torres (Marketing AO); the direct request is refused and the request stays in FOR_MKT_APPROVAL.</t>
         </is>
       </c>
       <c r="K69" s="12" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="F70" s="12" t="inlineStr">
         <is>
-          <t>mkttl</t>
+          <t>Marites Hernandez</t>
         </is>
       </c>
       <c r="G70" s="12" t="inlineStr">
@@ -14620,7 +14620,7 @@
       </c>
       <c r="H70" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as mkttl; Package Requests, For Approval tab; open the request.
+          <t>1. Log in as Marites Hernandez (Marketing TL / TH / UH); Package Requests, For Approval tab; open the request.
 2. Click Approve and send to TSU with comment "OK for TSU".
 3. Open the TSU Review tab.</t>
         </is>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="J70" s="12" t="inlineStr">
         <is>
-          <t>The request is in FOR_TSU_REVIEW and listed in the TSU Review tab; the history shows the approval by mkttl with the comment.</t>
+          <t>The request is in FOR_TSU_REVIEW and listed in the TSU Review tab; the history shows the approval by Marites Hernandez (Marketing TL / TH / UH) with the comment.</t>
         </is>
       </c>
       <c r="K70" s="12" t="inlineStr">
@@ -14693,7 +14693,7 @@
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>mkttl</t>
+          <t>Marites Hernandez</t>
         </is>
       </c>
       <c r="G71" s="12" t="inlineStr">
@@ -14703,8 +14703,8 @@
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>1. As mkttl open a request in FOR_MKT_APPROVAL; click Return to requester; select Incomplete or incorrect details; comment "add the loss history"; confirm.
-2. As ao open the request.</t>
+          <t>1. As Marites Hernandez (Marketing TL / TH / UH) open a request in FOR_MKT_APPROVAL; click Return to requester; select Incomplete or incorrect details; comment "add the loss history"; confirm.
+2. As Aileen Torres (Marketing AO) open the request.</t>
         </is>
       </c>
       <c r="I71" s="12" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="J71" s="12" t="inlineStr">
         <is>
-          <t>The request is back in DRAFT; the reason and comment are shown on the request and ao is notified.</t>
+          <t>The request is back in DRAFT; the reason and comment are shown on the request and Aileen Torres (Marketing AO) is notified.</t>
         </is>
       </c>
       <c r="K71" s="12" t="inlineStr">
@@ -14775,7 +14775,7 @@
       </c>
       <c r="F72" s="12" t="inlineStr">
         <is>
-          <t>mkttl</t>
+          <t>Marites Hernandez</t>
         </is>
       </c>
       <c r="G72" s="12" t="inlineStr">
@@ -14857,7 +14857,7 @@
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G73" s="12" t="inlineStr">
@@ -14868,7 +14868,7 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>1. As mbs send a direct request to save the request with the same content.</t>
+          <t>1. As Monica Vergara (Marketing Business Services) send a direct request to save the request with the same content.</t>
         </is>
       </c>
       <c r="I73" s="12" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G74" s="12" t="inlineStr">
@@ -14950,7 +14950,7 @@
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as tsulead; TSU Workbench; open PKR-2026-900002.
+          <t>1. Log in as Teresa Villareal (TSU Team Lead); TSU Workbench; open PKR-2026-900002.
 2. Click Recommend for approval; leave the text blank (spaces only); confirm.</t>
         </is>
       </c>
@@ -15023,7 +15023,7 @@
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="J75" s="12" t="inlineStr">
         <is>
-          <t>The request moves to FOR_TSU_APPROVAL; the TSU Head queue shows it; tsuhead is notified.</t>
+          <t>The request moves to FOR_TSU_APPROVAL; the TSU Head queue shows it; Tomas Vergara (TSU Head) is notified.</t>
         </is>
       </c>
       <c r="K75" s="12" t="inlineStr">
@@ -15104,7 +15104,7 @@
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G76" s="12" t="inlineStr">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as tsuhead; open PKR-2026-900002.</t>
+          <t>1. Log in as Tomas Vergara (TSU Head); open PKR-2026-900002.</t>
         </is>
       </c>
       <c r="I76" s="12" t="inlineStr">
@@ -15124,7 +15124,7 @@
       </c>
       <c r="J76" s="12" t="inlineStr">
         <is>
-          <t>The milestone TSU recommendation shows the text, tsulead and the time.</t>
+          <t>The milestone TSU recommendation shows the text, Teresa Villareal (TSU Team Lead) and the time.</t>
         </is>
       </c>
       <c r="K76" s="12" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G77" s="12" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="J77" s="12" t="inlineStr">
         <is>
-          <t>The change is saved and recorded in the history with tsulead as user; the stage does not change.</t>
+          <t>The change is saved and recorded in the history with Teresa Villareal (TSU Team Lead) as user; the stage does not change.</t>
         </is>
       </c>
       <c r="K77" s="12" t="inlineStr">
@@ -15266,7 +15266,7 @@
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G78" s="12" t="inlineStr">
@@ -15286,7 +15286,7 @@
       </c>
       <c r="J78" s="12" t="inlineStr">
         <is>
-          <t>The request is back in DRAFT with the reason; ao is notified.</t>
+          <t>The request is back in DRAFT with the reason; Aileen Torres (Marketing AO) is notified.</t>
         </is>
       </c>
       <c r="K78" s="12" t="inlineStr">
@@ -15347,18 +15347,18 @@
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>tsulead recommended the request; tsulead also holds PKG_TSU_APPROVE in the test set-up (test lead grants it for this case only).
+          <t>Teresa Villareal (TSU Team Lead) recommended the request; Teresa Villareal (TSU Team Lead) also holds PKG_TSU_APPROVE in the test set-up (test lead grants it for this case only).
 Data: TD-PM-12 New CGL request keyed in the test</t>
         </is>
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>1. As tsulead click Approve for negotiation.</t>
+          <t>1. As Teresa Villareal (TSU Team Lead) click Approve for negotiation.</t>
         </is>
       </c>
       <c r="I79" s="12" t="inlineStr">
@@ -15430,7 +15430,7 @@
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G80" s="12" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="H80" s="12" t="inlineStr">
         <is>
-          <t>1. As tsuhead open the recommended request of TD-PM-12; click Approve for negotiation.
+          <t>1. As Tomas Vergara (TSU Head) open the recommended request of TD-PM-12; click Approve for negotiation.
 2. Open the Negotiation tab.</t>
         </is>
       </c>
@@ -15512,18 +15512,18 @@
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>A Retire package request on MTR32 recommended by tsulead.
+          <t>A Retire package request on MTR32 recommended by Teresa Villareal (TSU Team Lead).
 Data: TD-PM-12 New CGL request keyed in the test</t>
         </is>
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>1. As tsuhead click Approve without negotiation.</t>
+          <t>1. As Tomas Vergara (TSU Head) click Approve without negotiation.</t>
         </is>
       </c>
       <c r="I81" s="12" t="inlineStr">
@@ -15533,7 +15533,7 @@
       </c>
       <c r="J81" s="12" t="inlineStr">
         <is>
-          <t>The request moves to FOR_MANCOM; the Negotiation tab has no round; mancom is notified.</t>
+          <t>The request moves to FOR_MANCOM; the Negotiation tab has no round; Manuel Uy (ManCom member) is notified.</t>
         </is>
       </c>
       <c r="K81" s="12" t="inlineStr">
@@ -15594,7 +15594,7 @@
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G82" s="12" t="inlineStr">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="H82" s="12" t="inlineStr">
         <is>
-          <t>1. As tsuhead open the request and look at the actions; send a direct request for the workflow action Approve.</t>
+          <t>1. As Tomas Vergara (TSU Head) open the request and look at the actions; send a direct request for the workflow action Approve.</t>
         </is>
       </c>
       <c r="I82" s="12" t="inlineStr">
@@ -15676,7 +15676,7 @@
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G83" s="12" t="inlineStr">
@@ -15686,7 +15686,7 @@
       </c>
       <c r="H83" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as tsulead; Package Requests; open each tab from Drafts to Closed.</t>
+          <t>1. Log in as Teresa Villareal (TSU Team Lead); Package Requests; open each tab from Drafts to Closed.</t>
         </is>
       </c>
       <c r="I83" s="12" t="inlineStr">
@@ -15757,7 +15757,7 @@
       </c>
       <c r="F84" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G84" s="12" t="inlineStr">
@@ -15767,7 +15767,7 @@
       </c>
       <c r="H84" s="12" t="inlineStr">
         <is>
-          <t>1. Search "900003"; clear; filter Type = Renew package; clear; tick Mine only as ao.</t>
+          <t>1. Search "900003"; clear; filter Type = Renew package; clear; tick Mine only as Aileen Torres (Marketing AO).</t>
         </is>
       </c>
       <c r="I84" s="12" t="inlineStr">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="J84" s="12" t="inlineStr">
         <is>
-          <t>Each filter returns only the matching requests (900003; 900005; the requests created by ao).</t>
+          <t>Each filter returns only the matching requests (900003; 900005; the requests created by Aileen Torres (Marketing AO)).</t>
         </is>
       </c>
       <c r="K84" s="12" t="inlineStr">
@@ -15838,7 +15838,7 @@
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -15848,8 +15848,8 @@
       </c>
       <c r="H85" s="12" t="inlineStr">
         <is>
-          <t>1. As mkttl approve a submitted request.
-2. As tsulead open the notification bell.</t>
+          <t>1. As Marites Hernandez (Marketing TL / TH / UH) approve a submitted request.
+2. As Teresa Villareal (TSU Team Lead) open the notification bell.</t>
         </is>
       </c>
       <c r="I85" s="12" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G86" s="12" t="inlineStr">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="H86" s="12" t="inlineStr">
         <is>
-          <t>1. As tsulead select two requests in the Negotiation queue; click Assign; choose tsu.</t>
+          <t>1. As Teresa Villareal (TSU Team Lead) select two requests in the Negotiation queue; click Assign; choose Teodoro Valdez (TSU Officer).</t>
         </is>
       </c>
       <c r="I86" s="12" t="inlineStr">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="J86" s="12" t="inlineStr">
         <is>
-          <t>Both requests show tsu as assignee; the assignment is recorded on each work case.</t>
+          <t>Both requests show Teodoro Valdez (TSU Officer) as assignee; the assignment is recorded on each work case.</t>
         </is>
       </c>
       <c r="K86" s="12" t="inlineStr">
@@ -16001,7 +16001,7 @@
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G87" s="12" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="H87" s="12" t="inlineStr">
         <is>
-          <t>1. As tsu open an unassigned request in the TSU Workbench; click Claim.</t>
+          <t>1. As Teodoro Valdez (TSU Officer) open an unassigned request in the TSU Workbench; click Claim.</t>
         </is>
       </c>
       <c r="I87" s="12" t="inlineStr">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="J87" s="12" t="inlineStr">
         <is>
-          <t>tsu becomes the assignee.</t>
+          <t>Teodoro Valdez (TSU Officer) becomes the assignee.</t>
         </is>
       </c>
       <c r="K87" s="12" t="inlineStr">
@@ -16082,7 +16082,7 @@
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G88" s="12" t="inlineStr">
@@ -16164,7 +16164,7 @@
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G89" s="12" t="inlineStr">
@@ -16174,8 +16174,8 @@
       </c>
       <c r="H89" s="12" t="inlineStr">
         <is>
-          <t>1. As tsu open round 1; select INS-MGIC and INS-LAC; click Submit for approval.
-2. As tsu click Approve and send.</t>
+          <t>1. As Teodoro Valdez (TSU Officer) open round 1; select INS-MGIC and INS-LAC; click Submit for approval.
+2. As Teodoro Valdez (TSU Officer) click Approve and send.</t>
         </is>
       </c>
       <c r="I89" s="12" t="inlineStr">
@@ -16185,7 +16185,7 @@
       </c>
       <c r="J89" s="12" t="inlineStr">
         <is>
-          <t>The QS gets a number PQS-2026-nnnnnn and status For approval; tsu's approval is refused.
+          <t>The QS gets a number PQS-2026-nnnnnn and status For approval; Teodoro Valdez (TSU Officer)'s approval is refused.
 Message "The quotation slip is approved by a TL or a co-officer" (QS_FOUR_EYES).</t>
         </is>
       </c>
@@ -16247,7 +16247,7 @@
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G90" s="12" t="inlineStr">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="H90" s="12" t="inlineStr">
         <is>
-          <t>1. As tsulead open round 1; review the QS PDF; click Approve and send.
+          <t>1. As Teresa Villareal (TSU Team Lead) open round 1; review the QS PDF; click Approve and send.
 2. Open the E-mails tab.</t>
         </is>
       </c>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G91" s="12" t="inlineStr">
@@ -16410,7 +16410,7 @@
       </c>
       <c r="F92" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G92" s="12" t="inlineStr">
@@ -16493,7 +16493,7 @@
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G93" s="12" t="inlineStr">
@@ -16575,7 +16575,7 @@
       </c>
       <c r="F94" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G94" s="12" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G95" s="12" t="inlineStr">
@@ -16739,7 +16739,7 @@
       </c>
       <c r="F96" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G96" s="12" t="inlineStr">
@@ -16821,7 +16821,7 @@
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G97" s="12" t="inlineStr">
@@ -16902,7 +16902,7 @@
       </c>
       <c r="F98" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G98" s="12" t="inlineStr">
@@ -16984,7 +16984,7 @@
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G99" s="12" t="inlineStr">
@@ -17066,7 +17066,7 @@
       </c>
       <c r="F100" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G100" s="12" t="inlineStr">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G101" s="12" t="inlineStr">
@@ -17168,7 +17168,7 @@
       </c>
       <c r="J101" s="12" t="inlineStr">
         <is>
-          <t>The history lists 0.34 and 0.33 with user tsu and the times.</t>
+          <t>The history lists 0.34 and 0.33 with user Teodoro Valdez (TSU Officer) and the times.</t>
         </is>
       </c>
       <c r="K101" s="12" t="inlineStr">
@@ -17229,7 +17229,7 @@
       </c>
       <c r="F102" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G102" s="12" t="inlineStr">
@@ -17310,7 +17310,7 @@
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G103" s="12" t="inlineStr">
@@ -17392,7 +17392,7 @@
       </c>
       <c r="F104" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G104" s="12" t="inlineStr">
@@ -17475,7 +17475,7 @@
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G105" s="12" t="inlineStr">
@@ -17557,7 +17557,7 @@
       </c>
       <c r="F106" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G106" s="12" t="inlineStr">
@@ -17639,7 +17639,7 @@
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G107" s="12" t="inlineStr">
@@ -17650,7 +17650,7 @@
       <c r="H107" s="12" t="inlineStr">
         <is>
           <t>1. On PRF-2026-900004 open the Comparative Table; Add Option for Luzon Assurance Co. with the response Approved; key the Final Terms for Proposal.
-2. As ao select Mabuhay General Insurance Corp. and Luzon Assurance Co. and Proceed to Proposal; as tsu generate the proposal.</t>
+2. As Aileen Torres (Marketing AO) select Mabuhay General Insurance Corp. and Luzon Assurance Co. and Proceed to Proposal; as Teodoro Valdez (TSU Officer) generate the proposal.</t>
         </is>
       </c>
       <c r="I107" s="12" t="inlineStr">
@@ -17721,7 +17721,7 @@
       </c>
       <c r="F108" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G108" s="12" t="inlineStr">
@@ -17802,7 +17802,7 @@
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G109" s="12" t="inlineStr">
@@ -17884,7 +17884,7 @@
       </c>
       <c r="F110" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G110" s="12" t="inlineStr">
@@ -17967,7 +17967,7 @@
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G111" s="12" t="inlineStr">
@@ -18049,7 +18049,7 @@
       </c>
       <c r="F112" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G112" s="12" t="inlineStr">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G113" s="12" t="inlineStr">
@@ -18213,7 +18213,7 @@
       </c>
       <c r="F114" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G114" s="12" t="inlineStr">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G115" s="12" t="inlineStr">
@@ -18376,7 +18376,7 @@
       </c>
       <c r="F116" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G116" s="12" t="inlineStr">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G117" s="12" t="inlineStr">
@@ -18467,7 +18467,7 @@
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as ao2; open PKR-2026-900003, Comparative tab.</t>
+          <t>1. Log in as another Marketing AO; open PKR-2026-900003, Comparative tab.</t>
         </is>
       </c>
       <c r="I117" s="12" t="inlineStr">
@@ -18538,7 +18538,7 @@
       </c>
       <c r="F118" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G118" s="12" t="inlineStr">
@@ -18548,7 +18548,7 @@
       </c>
       <c r="H118" s="12" t="inlineStr">
         <is>
-          <t>1. Send a direct request to compile the master comparative, signed in as ao2.</t>
+          <t>1. Send a direct request to compile the master comparative, signed in as another Marketing AO.</t>
         </is>
       </c>
       <c r="I118" s="12" t="inlineStr">
@@ -18620,7 +18620,7 @@
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G119" s="12" t="inlineStr">
@@ -18702,7 +18702,7 @@
       </c>
       <c r="F120" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G120" s="12" t="inlineStr">
@@ -18784,7 +18784,7 @@
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G121" s="12" t="inlineStr">
@@ -18865,7 +18865,7 @@
       </c>
       <c r="F122" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G122" s="12" t="inlineStr">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G123" s="12" t="inlineStr">
@@ -19029,7 +19029,7 @@
       </c>
       <c r="F124" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G124" s="12" t="inlineStr">
@@ -19111,7 +19111,7 @@
       </c>
       <c r="F125" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G125" s="12" t="inlineStr">
@@ -19122,7 +19122,7 @@
       </c>
       <c r="H125" s="12" t="inlineStr">
         <is>
-          <t>1. As tsuhead send a direct request for the action Proceed to requirements (generic package).</t>
+          <t>1. As Tomas Vergara (TSU Head) send a direct request for the action Proceed to requirements (generic package).</t>
         </is>
       </c>
       <c r="I125" s="12" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="F126" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G126" s="12" t="inlineStr">
@@ -19214,7 +19214,7 @@
       </c>
       <c r="J126" s="12" t="inlineStr">
         <is>
-          <t>The request is in FOR_MKT_REVIEW; ao2 (requester) is notified.</t>
+          <t>The request is in FOR_MKT_REVIEW; another Marketing AO (requester) is notified.</t>
         </is>
       </c>
       <c r="K126" s="12" t="inlineStr">
@@ -19275,7 +19275,7 @@
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G127" s="12" t="inlineStr">
@@ -19358,7 +19358,7 @@
       </c>
       <c r="F128" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G128" s="12" t="inlineStr">
@@ -19439,7 +19439,7 @@
       </c>
       <c r="F129" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G129" s="12" t="inlineStr">
@@ -19449,9 +19449,9 @@
       </c>
       <c r="H129" s="12" t="inlineStr">
         <is>
-          <t>1. As ao2 open the request in FOR_MKT_REVIEW; click Request changes; reason Additional insurer requirements; comment "client wants a lower rate".
-2. As tsu make the terms final again; as tsuhead release to Marketing.
-3. As ao2 click Accept terms with comment "client agrees".</t>
+          <t>1. As another Marketing AO open the request in FOR_MKT_REVIEW; click Request changes; reason Additional insurer requirements; comment "client wants a lower rate".
+2. As Teodoro Valdez (TSU Officer) make the terms final again; as Tomas Vergara (TSU Head) release to Marketing.
+3. As another Marketing AO click Accept terms with comment "client agrees".</t>
         </is>
       </c>
       <c r="I129" s="12" t="inlineStr">
@@ -19522,7 +19522,7 @@
       </c>
       <c r="F130" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G130" s="12" t="inlineStr">
@@ -19604,7 +19604,7 @@
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G131" s="12" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="F132" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G132" s="12" t="inlineStr">
@@ -19770,7 +19770,7 @@
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G133" s="12" t="inlineStr">
@@ -19791,7 +19791,7 @@
       </c>
       <c r="J133" s="12" t="inlineStr">
         <is>
-          <t>The package slip shows the rate scheme, insurers and coverages; after upload the checklist is complete; the request is in FOR_MANCOM and mancom is notified.</t>
+          <t>The package slip shows the rate scheme, insurers and coverages; after upload the checklist is complete; the request is in FOR_MANCOM and Manuel Uy (ManCom member) is notified.</t>
         </is>
       </c>
       <c r="K133" s="12" t="inlineStr">
@@ -19852,7 +19852,7 @@
       </c>
       <c r="F134" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G134" s="12" t="inlineStr">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G135" s="12" t="inlineStr">
@@ -20016,7 +20016,7 @@
       </c>
       <c r="F136" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G136" s="12" t="inlineStr">
@@ -20027,7 +20027,7 @@
       <c r="H136" s="12" t="inlineStr">
         <is>
           <t>1. On PKR-2026-900004 open Routing &amp; Approvals; select the ManCom member and the President; Send for ManCom Approval.
-2. As mancom approve; as the President approve.</t>
+2. As Manuel Uy (ManCom member) approve; as the President approve.</t>
         </is>
       </c>
       <c r="I136" s="12" t="inlineStr">
@@ -20098,7 +20098,7 @@
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>mancom</t>
+          <t>Manuel Uy</t>
         </is>
       </c>
       <c r="G137" s="12" t="inlineStr">
@@ -20179,7 +20179,7 @@
       </c>
       <c r="F138" s="12" t="inlineStr">
         <is>
-          <t>mancom</t>
+          <t>Manuel Uy</t>
         </is>
       </c>
       <c r="G138" s="12" t="inlineStr">
@@ -20189,7 +20189,7 @@
       </c>
       <c r="H138" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as mancom; open PKR-2026-900004; Requirements &amp; Sign-off tab.
+          <t>1. Log in as Manuel Uy (ManCom member); open PKR-2026-900004; Requirements &amp; Sign-off tab.
 2. Upload the signed ManCom sheet; click Sign off and send to MBS with comment "signed".</t>
         </is>
       </c>
@@ -20200,7 +20200,7 @@
       </c>
       <c r="J138" s="12" t="inlineStr">
         <is>
-          <t>The request is in WITH_MBS; the decision SIGNED shows mancom, time and the sheet; mbs is notified.</t>
+          <t>The request is in WITH_MBS; the decision SIGNED shows Manuel Uy (ManCom member), time and the sheet; Monica Vergara (Marketing Business Services) is notified.</t>
         </is>
       </c>
       <c r="K138" s="12" t="inlineStr">
@@ -20261,7 +20261,7 @@
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
@@ -20271,8 +20271,8 @@
       </c>
       <c r="H139" s="12" t="inlineStr">
         <is>
-          <t>1. As tsu send a direct request to sign off PKR-2026-900004.
-2. As mbs send a direct request to set up the package version of the same request before sign-off.</t>
+          <t>1. As Teodoro Valdez (TSU Officer) send a direct request to sign off PKR-2026-900004.
+2. As Monica Vergara (Marketing Business Services) send a direct request to set up the package version of the same request before sign-off.</t>
         </is>
       </c>
       <c r="I139" s="12" t="inlineStr">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="F140" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G140" s="12" t="inlineStr">
@@ -20354,7 +20354,7 @@
       </c>
       <c r="H140" s="12" t="inlineStr">
         <is>
-          <t>1. As tsu open the Negotiation tab of the signed-off request; try to resend a QS.</t>
+          <t>1. As Teodoro Valdez (TSU Officer) open the Negotiation tab of the signed-off request; try to resend a QS.</t>
         </is>
       </c>
       <c r="I140" s="12" t="inlineStr">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>mancom</t>
+          <t>Manuel Uy</t>
         </is>
       </c>
       <c r="G141" s="12" t="inlineStr">
@@ -20507,7 +20507,7 @@
       </c>
       <c r="F142" s="12" t="inlineStr">
         <is>
-          <t>mancom</t>
+          <t>Manuel Uy</t>
         </is>
       </c>
       <c r="G142" s="12" t="inlineStr">
@@ -20590,7 +20590,7 @@
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>mancom</t>
+          <t>Manuel Uy</t>
         </is>
       </c>
       <c r="G143" s="12" t="inlineStr">
@@ -20610,7 +20610,7 @@
       </c>
       <c r="J143" s="12" t="inlineStr">
         <is>
-          <t>The request is in REQUIREMENTS_PREP; a RETURNED decision is recorded; tsu is notified.</t>
+          <t>The request is in REQUIREMENTS_PREP; a RETURNED decision is recorded; Teodoro Valdez (TSU Officer) is notified.</t>
         </is>
       </c>
       <c r="K143" s="12" t="inlineStr">
@@ -20671,7 +20671,7 @@
       </c>
       <c r="F144" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G144" s="12" t="inlineStr">
@@ -20681,7 +20681,7 @@
       </c>
       <c r="H144" s="12" t="inlineStr">
         <is>
-          <t>1. As mbs send a direct request to set up the package version of PKR-2026-900004 (FOR_MANCOM).</t>
+          <t>1. As Monica Vergara (Marketing Business Services) send a direct request to set up the package version of PKR-2026-900004 (FOR_MANCOM).</t>
         </is>
       </c>
       <c r="I144" s="12" t="inlineStr">
@@ -20753,7 +20753,7 @@
       </c>
       <c r="F145" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G145" s="12" t="inlineStr">
@@ -20835,7 +20835,7 @@
       </c>
       <c r="F146" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G146" s="12" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G147" s="12" t="inlineStr">
@@ -20936,7 +20936,7 @@
       </c>
       <c r="J147" s="12" t="inlineStr">
         <is>
-          <t>The request is in REQUIREMENTS_PREP; tsu is notified and sees the reason.</t>
+          <t>The request is in REQUIREMENTS_PREP; Teodoro Valdez (TSU Officer) is notified and sees the reason.</t>
         </is>
       </c>
       <c r="K147" s="12" t="inlineStr">
@@ -20997,7 +20997,7 @@
       </c>
       <c r="F148" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G148" s="12" t="inlineStr">
@@ -21079,7 +21079,7 @@
       </c>
       <c r="F149" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G149" s="12" t="inlineStr">
@@ -21161,7 +21161,7 @@
       </c>
       <c r="F150" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G150" s="12" t="inlineStr">
@@ -21243,7 +21243,7 @@
       </c>
       <c r="F151" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G151" s="12" t="inlineStr">
@@ -21253,8 +21253,8 @@
       </c>
       <c r="H151" s="12" t="inlineStr">
         <is>
-          <t>1. As mbs submit MTR12 v2 for validation.
-2. As mbs send a direct request to validate version 2 of MTR12.</t>
+          <t>1. As Monica Vergara (Marketing Business Services) submit MTR12 v2 for validation.
+2. As Monica Vergara (Marketing Business Services) send a direct request to validate version 2 of MTR12.</t>
         </is>
       </c>
       <c r="I151" s="12" t="inlineStr">
@@ -21264,7 +21264,7 @@
       </c>
       <c r="J151" s="12" t="inlineStr">
         <is>
-          <t>The request is refused (mbs does not hold PRODUCT_VALIDATE); the version stays FOR_VALIDATION.</t>
+          <t>The request is refused (Monica Vergara (Marketing Business Services) does not hold PRODUCT_VALIDATE); the version stays FOR_VALIDATION.</t>
         </is>
       </c>
       <c r="K151" s="12" t="inlineStr">
@@ -21325,18 +21325,18 @@
       </c>
       <c r="F152" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Garcia</t>
         </is>
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
-          <t>badmin also holds PRODUCT_MAINTAIN for this case and submitted the version.
+          <t>Bea Garcia (Business Administrator) also holds PRODUCT_MAINTAIN for this case and submitted the version.
 Data: TD-PM-08 Draft package version</t>
         </is>
       </c>
       <c r="H152" s="12" t="inlineStr">
         <is>
-          <t>1. As badmin click Validate and release.</t>
+          <t>1. As Bea Garcia (Business Administrator) click Validate and release.</t>
         </is>
       </c>
       <c r="I152" s="12" t="inlineStr">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G153" s="12" t="inlineStr">
@@ -21430,7 +21430,7 @@
       </c>
       <c r="J153" s="12" t="inlineStr">
         <is>
-          <t>Version 2 is RELEASED from its effective date; version 1 ends the day before; the checklist, tsuhead and the time are recorded; the linked request is RELEASED and an advisory draft exists.</t>
+          <t>Version 2 is RELEASED from its effective date; version 1 ends the day before; the checklist, Tomas Vergara (TSU Head) and the time are recorded; the linked request is RELEASED and an advisory draft exists.</t>
         </is>
       </c>
       <c r="K153" s="12" t="inlineStr">
@@ -21491,7 +21491,7 @@
       </c>
       <c r="F154" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G154" s="12" t="inlineStr">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
@@ -21592,7 +21592,7 @@
       </c>
       <c r="J155" s="12" t="inlineStr">
         <is>
-          <t>The version is DRAFT and editable; the request is back in WITH_MBS; mbs is notified.</t>
+          <t>The version is DRAFT and editable; the request is back in WITH_MBS; Monica Vergara (Marketing Business Services) is notified.</t>
         </is>
       </c>
       <c r="K155" s="12" t="inlineStr">
@@ -21653,7 +21653,7 @@
       </c>
       <c r="F156" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G156" s="12" t="inlineStr">
@@ -21735,7 +21735,7 @@
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G157" s="12" t="inlineStr">
@@ -21817,7 +21817,7 @@
       </c>
       <c r="F158" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G158" s="12" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G159" s="12" t="inlineStr">
@@ -21980,7 +21980,7 @@
       </c>
       <c r="F160" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G160" s="12" t="inlineStr">
@@ -22063,7 +22063,7 @@
       </c>
       <c r="F161" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G161" s="12" t="inlineStr">
@@ -22075,7 +22075,7 @@
         <is>
           <t>1. Upload the signed package slip.
 2. Edit the advisory - groups Marketing and Operations, e-mail operations@uat.brokerverse.cloud, subject "MTR15 renewed", text; save.
-3. Click Send. As ao open the notification bell.</t>
+3. Click Send. As Aileen Torres (Marketing AO) open the notification bell.</t>
         </is>
       </c>
       <c r="I161" s="12" t="inlineStr">
@@ -22085,7 +22085,7 @@
       </c>
       <c r="J161" s="12" t="inlineStr">
         <is>
-          <t>The advisory is SENT; ao and the Operations users have an in-app notification; one protected e-mail is logged; the advisory PDF is stored on the request and lists the signed slip and the ManCom sign-off.</t>
+          <t>The advisory is SENT; Aileen Torres (Marketing AO) and the Operations users have an in-app notification; one protected e-mail is logged; the advisory PDF is stored on the request and lists the signed slip and the ManCom sign-off.</t>
         </is>
       </c>
       <c r="K161" s="12" t="inlineStr">
@@ -22146,7 +22146,7 @@
       </c>
       <c r="F162" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G162" s="12" t="inlineStr">
@@ -22227,7 +22227,7 @@
       </c>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G163" s="12" t="inlineStr">
@@ -22309,7 +22309,7 @@
       </c>
       <c r="F164" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G164" s="12" t="inlineStr">
@@ -22391,7 +22391,7 @@
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G165" s="12" t="inlineStr">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="F166" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G166" s="12" t="inlineStr">
@@ -22483,7 +22483,7 @@
       </c>
       <c r="H166" s="12" t="inlineStr">
         <is>
-          <t>1. Send a direct request to send an advisory, signed in as ao.</t>
+          <t>1. Send a direct request to send an advisory, signed in as Aileen Torres (Marketing AO).</t>
         </is>
       </c>
       <c r="I166" s="12" t="inlineStr">
@@ -22555,7 +22555,7 @@
       </c>
       <c r="F167" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G167" s="12" t="inlineStr">
@@ -22565,8 +22565,8 @@
       </c>
       <c r="H167" s="12" t="inlineStr">
         <is>
-          <t>1. As mbs open product CAR02, click Deactivate Package, enter an effective date 30 days ahead, the reason Replaced by another package and the approver tsuhead; Submit for Approval.
-2. As tsuhead open Deactivation Requests, View Details, Approve.</t>
+          <t>1. As Monica Vergara (Marketing Business Services) open product CAR02, click Deactivate Package, enter an effective date 30 days ahead, the reason Replaced by another package and the approver Tomas Vergara (TSU Head); Submit for Approval.
+2. As Tomas Vergara (TSU Head) open Deactivation Requests, View Details, Approve.</t>
         </is>
       </c>
       <c r="I167" s="12" t="inlineStr">
@@ -22637,7 +22637,7 @@
       </c>
       <c r="F168" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G168" s="12" t="inlineStr">
@@ -22718,12 +22718,12 @@
       </c>
       <c r="F169" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>Retire package request on MTR32 signed off by mancom (With MBS for set-up).
+          <t>Retire package request on MTR32 signed off by Manuel Uy (ManCom member).
 Data: TD-PM-11 Catalogue and insurer panel</t>
         </is>
       </c>
@@ -22800,7 +22800,7 @@
       </c>
       <c r="F170" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G170" s="12" t="inlineStr">
@@ -22882,7 +22882,7 @@
       </c>
       <c r="F171" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G171" s="12" t="inlineStr">
@@ -22964,7 +22964,7 @@
       </c>
       <c r="F172" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G172" s="12" t="inlineStr">
@@ -23046,7 +23046,7 @@
       </c>
       <c r="F173" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Auditor</t>
         </is>
       </c>
       <c r="G173" s="12" t="inlineStr">
@@ -23056,7 +23056,7 @@
       </c>
       <c r="H173" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as auditor; Products; filter Retired; open MTR32.</t>
+          <t>1. Log in as the Auditor; Products; filter Retired; open MTR32.</t>
         </is>
       </c>
       <c r="I173" s="12" t="inlineStr">
@@ -23127,7 +23127,7 @@
       </c>
       <c r="F174" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G174" s="12" t="inlineStr">
@@ -23138,7 +23138,7 @@
       <c r="H174" s="12" t="inlineStr">
         <is>
           <t>1. Open product MTR10; Versions tab; click New Version.
-2. Change the package rate; save; submit; have tsuhead validate and release it.</t>
+2. Change the package rate; save; submit; have Tomas Vergara (TSU Head) validate and release it.</t>
         </is>
       </c>
       <c r="I174" s="12" t="inlineStr">
@@ -23209,7 +23209,7 @@
       </c>
       <c r="F175" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G175" s="12" t="inlineStr">
@@ -23290,7 +23290,7 @@
       </c>
       <c r="F176" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G176" s="12" t="inlineStr">
@@ -23372,7 +23372,7 @@
       </c>
       <c r="F177" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G177" s="12" t="inlineStr">
@@ -23454,7 +23454,7 @@
       </c>
       <c r="F178" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G178" s="12" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="H178" s="12" t="inlineStr">
         <is>
-          <t>1. As tsuhead send a direct request to create a version of MTR12.</t>
+          <t>1. As Tomas Vergara (TSU Head) send a direct request to create a version of MTR12.</t>
         </is>
       </c>
       <c r="I178" s="12" t="inlineStr">
@@ -23536,7 +23536,7 @@
       </c>
       <c r="F179" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G179" s="12" t="inlineStr">
@@ -23547,8 +23547,8 @@
       </c>
       <c r="H179" s="12" t="inlineStr">
         <is>
-          <t>1. As tsu create a package request of type Update for its existing risk code, with the terms of the signed slip; have it approved by Marketing and the TSU Team Lead.
-2. Upload the signed slip and record the ManCom reference; as mbs set up the version; as tsuhead validate and release it.</t>
+          <t>1. As Teodoro Valdez (TSU Officer) create a package request of type Update for its existing risk code, with the terms of the signed slip; have it approved by Marketing and the TSU Team Lead.
+2. Upload the signed slip and record the ManCom reference; as Monica Vergara (Marketing Business Services) set up the version; as Tomas Vergara (TSU Head) validate and release it.</t>
         </is>
       </c>
       <c r="I179" s="12" t="inlineStr">
@@ -23619,7 +23619,7 @@
       </c>
       <c r="F180" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G180" s="12" t="inlineStr">
@@ -23702,7 +23702,7 @@
       </c>
       <c r="F181" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G181" s="12" t="inlineStr">
@@ -23784,7 +23784,7 @@
       </c>
       <c r="F182" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G182" s="12" t="inlineStr">
@@ -23866,7 +23866,7 @@
       </c>
       <c r="F183" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G183" s="12" t="inlineStr">
@@ -23877,9 +23877,9 @@
       <c r="H183" s="12" t="inlineStr">
         <is>
           <t>1. Click Request Rate Exception; rate 2.50, reason "Loyal client"; submit.
-2. As approver open My Approvals and click the rate exception; the exception record opens.
+2. As Andres Bautista (New Business approver) open My Approvals and click the rate exception; the exception record opens.
 3. Check the requested rate against the scheme in force; click Approve, write a comment and confirm.
-4. As ao open the notice, then submit the quotation again.</t>
+4. As Aileen Torres (Marketing AO) open the notice, then submit the quotation again.</t>
         </is>
       </c>
       <c r="I183" s="12" t="inlineStr">
@@ -23950,7 +23950,7 @@
       </c>
       <c r="F184" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G184" s="12" t="inlineStr">
@@ -23960,7 +23960,7 @@
       </c>
       <c r="H184" s="12" t="inlineStr">
         <is>
-          <t>1. As approver open the pending exception from My Approvals; click Reject and leave the reason blank.</t>
+          <t>1. As Andres Bautista (New Business approver) open the pending exception from My Approvals; click Reject and leave the reason blank.</t>
         </is>
       </c>
       <c r="I184" s="12" t="inlineStr">
@@ -24032,7 +24032,7 @@
       </c>
       <c r="F185" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G185" s="12" t="inlineStr">
@@ -24042,8 +24042,8 @@
       </c>
       <c r="H185" s="12" t="inlineStr">
         <is>
-          <t>1. As approver open the pending exception; click Reject, write the reason and confirm.
-2. As ao open the quotation and submit it.</t>
+          <t>1. As Andres Bautista (New Business approver) open the pending exception; click Reject, write the reason and confirm.
+2. As Aileen Torres (Marketing AO) open the quotation and submit it.</t>
         </is>
       </c>
       <c r="I185" s="12" t="inlineStr">
@@ -24115,7 +24115,7 @@
       </c>
       <c r="F186" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G186" s="12" t="inlineStr">
@@ -24197,7 +24197,7 @@
       </c>
       <c r="F187" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G187" s="12" t="inlineStr">
@@ -24279,7 +24279,7 @@
       </c>
       <c r="F188" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G188" s="12" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="F189" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G189" s="12" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="F190" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G190" s="12" t="inlineStr">
@@ -24537,7 +24537,7 @@
       <c r="H191" s="12" t="inlineStr">
         <is>
           <t>1. Run the job PACKAGE_VERSION_LIFECYCLE from Administration &gt; Scheduled Jobs.
-2. As mbs filter Products by Expired.</t>
+2. As Monica Vergara (Marketing Business Services) filter Products by Expired.</t>
         </is>
       </c>
       <c r="I191" s="12" t="inlineStr">
@@ -24608,7 +24608,7 @@
       </c>
       <c r="F192" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G192" s="12" t="inlineStr">
@@ -24690,7 +24690,7 @@
       </c>
       <c r="F193" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Auditor</t>
         </is>
       </c>
       <c r="G193" s="12" t="inlineStr">
@@ -24700,7 +24700,7 @@
       </c>
       <c r="H193" s="12" t="inlineStr">
         <is>
-          <t>1. As auditor open PAR25 from the Expired filter; open its versions and a past request.</t>
+          <t>1. As the Auditor open PAR25 from the Expired filter; open its versions and a past request.</t>
         </is>
       </c>
       <c r="I193" s="12" t="inlineStr">
@@ -24771,7 +24771,7 @@
       </c>
       <c r="F194" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G194" s="12" t="inlineStr">
@@ -24781,7 +24781,7 @@
       </c>
       <c r="H194" s="12" t="inlineStr">
         <is>
-          <t>1. As ao open Products (no Expired filter shown); send a direct request to list the expired products.</t>
+          <t>1. As Aileen Torres (Marketing AO) open Products (no Expired filter shown); send a direct request to list the expired products.</t>
         </is>
       </c>
       <c r="I194" s="12" t="inlineStr">
@@ -24853,7 +24853,7 @@
       </c>
       <c r="F195" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G195" s="12" t="inlineStr">
@@ -24863,7 +24863,7 @@
       </c>
       <c r="H195" s="12" t="inlineStr">
         <is>
-          <t>1. As tsu open Package Expiry; Packages ending within (days) 60.</t>
+          <t>1. As Teodoro Valdez (TSU Officer) open Package Expiry; Packages ending within (days) 60.</t>
         </is>
       </c>
       <c r="I195" s="12" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="F196" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G196" s="12" t="inlineStr">
@@ -25027,7 +25027,7 @@
       <c r="H197" s="12" t="inlineStr">
         <is>
           <t>1. Run PACKAGE_EXPIRY_MONITOR twice on the same day.
-2. As tsu and mbs open the notification bell.</t>
+2. As Teodoro Valdez (TSU Officer) and Monica Vergara (Marketing Business Services) open the notification bell.</t>
         </is>
       </c>
       <c r="I197" s="12" t="inlineStr">
@@ -25098,7 +25098,7 @@
       </c>
       <c r="F198" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G198" s="12" t="inlineStr">
@@ -25179,7 +25179,7 @@
       </c>
       <c r="F199" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G199" s="12" t="inlineStr">
@@ -25260,7 +25260,7 @@
       </c>
       <c r="F200" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G200" s="12" t="inlineStr">
@@ -25270,7 +25270,7 @@
       </c>
       <c r="H200" s="12" t="inlineStr">
         <is>
-          <t>1. As ao send a direct request to open Package Expiry.</t>
+          <t>1. As Aileen Torres (Marketing AO) send a direct request to open Package Expiry.</t>
         </is>
       </c>
       <c r="I200" s="12" t="inlineStr">
@@ -25280,7 +25280,7 @@
       </c>
       <c r="J200" s="12" t="inlineStr">
         <is>
-          <t>The request is refused; the screen is not in ao's menu.
+          <t>The request is refused; the screen is not in Aileen Torres (Marketing AO)'s menu.
 Message "You are not permitted to perform this action" (ACCESS_DENIED).</t>
         </is>
       </c>
@@ -25354,7 +25354,7 @@
       <c r="H201" s="12" t="inlineStr">
         <is>
           <t>1. Run PACKAGE_EXPIRY_MONITOR; run it again the next day.
-2. As tsu open Package Expiry, tab Renewal in Progress.</t>
+2. As Teodoro Valdez (TSU Officer) open Package Expiry, tab Renewal in Progress.</t>
         </is>
       </c>
       <c r="I201" s="12" t="inlineStr">
@@ -25425,7 +25425,7 @@
       </c>
       <c r="F202" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G202" s="12" t="inlineStr">
@@ -25507,7 +25507,7 @@
       </c>
       <c r="F203" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G203" s="12" t="inlineStr">
@@ -25588,7 +25588,7 @@
       </c>
       <c r="F204" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G204" s="12" t="inlineStr">
@@ -25751,7 +25751,7 @@
       </c>
       <c r="F206" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G206" s="12" t="inlineStr">
@@ -25832,7 +25832,7 @@
       </c>
       <c r="F207" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G207" s="12" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="F208" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G208" s="12" t="inlineStr">
@@ -25995,7 +25995,7 @@
       </c>
       <c r="F209" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G209" s="12" t="inlineStr">
@@ -26005,7 +26005,7 @@
       </c>
       <c r="H209" s="12" t="inlineStr">
         <is>
-          <t>1. Log in as ao and open Product Maintenance Home.</t>
+          <t>1. Log in as Aileen Torres (Marketing AO) and open Product Maintenance Home.</t>
         </is>
       </c>
       <c r="I209" s="12" t="inlineStr">
@@ -26015,7 +26015,7 @@
       </c>
       <c r="J209" s="12" t="inlineStr">
         <is>
-          <t>The tiles show only the stages ao can see; no Versions for validation tile.</t>
+          <t>The tiles show only the stages Aileen Torres (Marketing AO) can see; no Versions for validation tile.</t>
         </is>
       </c>
       <c r="K209" s="12" t="inlineStr">
@@ -26076,7 +26076,7 @@
       </c>
       <c r="F210" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G210" s="12" t="inlineStr">
@@ -26158,7 +26158,7 @@
       </c>
       <c r="F211" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G211" s="12" t="inlineStr">
@@ -26239,7 +26239,7 @@
       </c>
       <c r="F212" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G212" s="12" t="inlineStr">
@@ -26320,7 +26320,7 @@
       </c>
       <c r="F213" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G213" s="12" t="inlineStr">
@@ -26401,7 +26401,7 @@
       </c>
       <c r="F214" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G214" s="12" t="inlineStr">
@@ -26482,7 +26482,7 @@
       </c>
       <c r="F215" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G215" s="12" t="inlineStr">
@@ -26563,7 +26563,7 @@
       </c>
       <c r="F216" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G216" s="12" t="inlineStr">
@@ -26573,7 +26573,7 @@
       </c>
       <c r="H216" s="12" t="inlineStr">
         <is>
-          <t>1. As ao open Reports; look for the three reports; send a direct run request of PM-PKG-STATUS.</t>
+          <t>1. As Aileen Torres (Marketing AO) open Reports; look for the three reports; send a direct run request of PM-PKG-STATUS.</t>
         </is>
       </c>
       <c r="I216" s="12" t="inlineStr">
@@ -26645,7 +26645,7 @@
       </c>
       <c r="F217" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G217" s="12" t="inlineStr">
@@ -26727,7 +26727,7 @@
       </c>
       <c r="F218" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G218" s="12" t="inlineStr">
@@ -26808,7 +26808,7 @@
       </c>
       <c r="F219" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="G219" s="12" t="inlineStr">
@@ -26890,7 +26890,7 @@
       </c>
       <c r="F220" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G220" s="12" t="inlineStr">
@@ -26900,7 +26900,7 @@
       </c>
       <c r="H220" s="12" t="inlineStr">
         <is>
-          <t>1. As mkttl approve a submitted request; as tsulead open the bell.</t>
+          <t>1. As Marites Hernandez (Marketing TL / TH / UH) approve a submitted request; as Teresa Villareal (TSU Team Lead) open the bell.</t>
         </is>
       </c>
       <c r="I220" s="12" t="inlineStr">
@@ -26971,7 +26971,7 @@
       </c>
       <c r="F221" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G221" s="12" t="inlineStr">
@@ -26981,7 +26981,7 @@
       </c>
       <c r="H221" s="12" t="inlineStr">
         <is>
-          <t>1. As tsu set the preference for stage entry to in-app and e-mail (Operations &gt; Notification Settings); trigger a stage entry for tsu.</t>
+          <t>1. As Teodoro Valdez (TSU Officer) set the preference for stage entry to in-app and e-mail (Operations &gt; Notification Settings); trigger a stage entry for Teodoro Valdez (TSU Officer).</t>
         </is>
       </c>
       <c r="I221" s="12" t="inlineStr">
@@ -26991,7 +26991,7 @@
       </c>
       <c r="J221" s="12" t="inlineStr">
         <is>
-          <t>tsu receives the in-app notification and an e-mail; with in-app only, no e-mail is sent.</t>
+          <t>Teodoro Valdez (TSU Officer) receives the in-app notification and an e-mail; with in-app only, no e-mail is sent.</t>
         </is>
       </c>
       <c r="K221" s="12" t="inlineStr">
@@ -27052,7 +27052,7 @@
       </c>
       <c r="F222" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="G222" s="12" t="inlineStr">
@@ -27072,7 +27072,7 @@
       </c>
       <c r="J222" s="12" t="inlineStr">
         <is>
-          <t>One change with product, version and effective date is listed on Product Master Transfers and sent in the file ProductMaster_&lt;yyyyMMddHHmmss&gt;.csv (in SIT and UAT, to the test account of BDOI's receiving system provided under the Integration scope).</t>
+          <t>One change with product, version and effective date is listed on Product Master Transfers and sent in the file ProductMaster_&lt;yyyyMMddHHmmss&gt;.csv (to the test account of BDOI's receiving system provided under the Integration scope in the test environment).</t>
         </is>
       </c>
       <c r="K222" s="12" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="F223" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G223" s="12" t="inlineStr">
@@ -27214,7 +27214,7 @@
       </c>
       <c r="F224" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G224" s="12" t="inlineStr">
@@ -27224,7 +27224,7 @@
       </c>
       <c r="H224" s="12" t="inlineStr">
         <is>
-          <t>1. As ao open the bell after the request of TC-PM-072.1-01 entered FOR_TSU_REVIEW.</t>
+          <t>1. As Aileen Torres (Marketing AO) open the bell after the request of TC-PM-072.1-01 entered FOR_TSU_REVIEW.</t>
         </is>
       </c>
       <c r="I224" s="12" t="inlineStr">
@@ -27234,7 +27234,7 @@
       </c>
       <c r="J224" s="12" t="inlineStr">
         <is>
-          <t>ao, who is not an owner of FOR_TSU_REVIEW, has no notification for that stage entry.</t>
+          <t>Aileen Torres (Marketing AO), who is not an owner of FOR_TSU_REVIEW, has no notification for that stage entry.</t>
         </is>
       </c>
       <c r="K224" s="12" t="inlineStr">
@@ -27295,7 +27295,7 @@
       </c>
       <c r="F225" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G225" s="12" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="H225" s="12" t="inlineStr">
         <is>
-          <t>1. As mbs send a direct request to set up the package version of PKR-2026-900004 (FOR_MANCOM).</t>
+          <t>1. As Monica Vergara (Marketing Business Services) send a direct request to set up the package version of PKR-2026-900004 (FOR_MANCOM).</t>
         </is>
       </c>
       <c r="I225" s="12" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="F226" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G226" s="12" t="inlineStr">
@@ -27387,7 +27387,7 @@
       </c>
       <c r="H226" s="12" t="inlineStr">
         <is>
-          <t>1. As tsu send a direct request for the workflow action Approve on a request in FOR_MKT_APPROVAL.</t>
+          <t>1. As Teodoro Valdez (TSU Officer) send a direct request for the workflow action Approve on a request in FOR_MKT_APPROVAL.</t>
         </is>
       </c>
       <c r="I226" s="12" t="inlineStr">
@@ -27469,7 +27469,7 @@
       </c>
       <c r="H227" s="12" t="inlineStr">
         <is>
-          <t>1. Leave PKR-2026-900002 in FOR_TSU_REVIEW beyond 24 hours; let the SLA check run; as tsulead open the bell.</t>
+          <t>1. Leave PKR-2026-900002 in FOR_TSU_REVIEW beyond 24 hours; let the SLA check run; as Teresa Villareal (TSU Team Lead) open the bell.</t>
         </is>
       </c>
       <c r="I227" s="12" t="inlineStr">
@@ -27479,7 +27479,7 @@
       </c>
       <c r="J227" s="12" t="inlineStr">
         <is>
-          <t>tsulead has an SLA alert for PKR-2026-900002; the request is red on the home page.</t>
+          <t>Teresa Villareal (TSU Team Lead) has an SLA alert for PKR-2026-900002; the request is red on the home page.</t>
         </is>
       </c>
       <c r="K227" s="12" t="inlineStr">
@@ -27540,7 +27540,7 @@
       </c>
       <c r="F228" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G228" s="12" t="inlineStr">
@@ -27622,7 +27622,7 @@
       </c>
       <c r="F229" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="G229" s="12" t="inlineStr">
@@ -27683,7 +27683,7 @@
       </c>
       <c r="B230" s="12" t="inlineStr">
         <is>
-          <t>New criterion authorised by badmin</t>
+          <t>New criterion authorised by Bea Garcia (Business Administrator)</t>
         </is>
       </c>
       <c r="C230" s="12" t="inlineStr">
@@ -27703,7 +27703,7 @@
       </c>
       <c r="F230" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G230" s="12" t="inlineStr">
@@ -27714,7 +27714,7 @@
       <c r="H230" s="12" t="inlineStr">
         <is>
           <t>1. Click New Criterion; code UAT1, name "UAT campaign", type Sales campaign, value basis Fixed amount, value 500, effective from today; products MTR12; save.
-2. As badmin authorise it in My Approvals.</t>
+2. As Bea Garcia (Business Administrator) authorise it in My Approvals.</t>
         </is>
       </c>
       <c r="I230" s="12" t="inlineStr">
@@ -27785,7 +27785,7 @@
       </c>
       <c r="F231" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G231" s="12" t="inlineStr">
@@ -27795,7 +27795,7 @@
       </c>
       <c r="H231" s="12" t="inlineStr">
         <is>
-          <t>1. As mbs open My Approvals.</t>
+          <t>1. As Monica Vergara (Marketing Business Services) open My Approvals.</t>
         </is>
       </c>
       <c r="I231" s="12" t="inlineStr">
@@ -27805,7 +27805,7 @@
       </c>
       <c r="J231" s="12" t="inlineStr">
         <is>
-          <t>UAT1 is not offered to mbs; a direct authorise request is refused.
+          <t>UAT1 is not offered to Monica Vergara (Marketing Business Services); a direct authorise request is refused.
 Message "A record cannot be authorized by the user who maintained it" (MAKER_CHECKER_VIOLATION).</t>
         </is>
       </c>
@@ -27867,7 +27867,7 @@
       </c>
       <c r="F232" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G232" s="12" t="inlineStr">
@@ -27949,7 +27949,7 @@
       </c>
       <c r="F233" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G233" s="12" t="inlineStr">
@@ -28031,7 +28031,7 @@
       </c>
       <c r="F234" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G234" s="12" t="inlineStr">
@@ -28113,7 +28113,7 @@
       </c>
       <c r="F235" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G235" s="12" t="inlineStr">
@@ -28195,7 +28195,7 @@
       </c>
       <c r="F236" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G236" s="12" t="inlineStr">
@@ -28277,7 +28277,7 @@
       </c>
       <c r="F237" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G237" s="12" t="inlineStr">
@@ -28288,7 +28288,7 @@
       <c r="H237" s="12" t="inlineStr">
         <is>
           <t>1. Open CPC2; click Amend; value 1.25, effective from next month; save.
-2. Check CPC2 before authorisation; authorise as badmin; check again.</t>
+2. Check CPC2 before authorisation; authorise as Bea Garcia (Business Administrator); check again.</t>
         </is>
       </c>
       <c r="I237" s="12" t="inlineStr">
@@ -28359,7 +28359,7 @@
       </c>
       <c r="F238" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G238" s="12" t="inlineStr">
@@ -28441,7 +28441,7 @@
       </c>
       <c r="F239" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G239" s="12" t="inlineStr">
@@ -28522,7 +28522,7 @@
       </c>
       <c r="F240" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G240" s="12" t="inlineStr">
@@ -28603,7 +28603,7 @@
       </c>
       <c r="F241" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G241" s="12" t="inlineStr">
@@ -28685,7 +28685,7 @@
       </c>
       <c r="F242" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G242" s="12" t="inlineStr">
@@ -28766,7 +28766,7 @@
       </c>
       <c r="F243" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G243" s="12" t="inlineStr">
@@ -28777,7 +28777,7 @@
       </c>
       <c r="H243" s="12" t="inlineStr">
         <is>
-          <t>1. Retire MTR32 (TC-PM-045.1-01); as mbs open the bell and Incentive Criteria.</t>
+          <t>1. Retire MTR32 (TC-PM-045.1-01); as Monica Vergara (Marketing Business Services) open the bell and Incentive Criteria.</t>
         </is>
       </c>
       <c r="I243" s="12" t="inlineStr">
@@ -28848,7 +28848,7 @@
       </c>
       <c r="F244" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Garcia</t>
         </is>
       </c>
       <c r="G244" s="12" t="inlineStr">
@@ -28930,17 +28930,17 @@
       </c>
       <c r="F245" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H245" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Product Maintenance Home.
 3. Compare the screen with SCR-PM-01 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.</t>
@@ -29012,17 +29012,17 @@
       </c>
       <c r="F246" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H246" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Package Requests.
 3. Compare the screen with SCR-PM-02 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.</t>
@@ -29094,17 +29094,17 @@
       </c>
       <c r="F247" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H247" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › New Package Request.
 3. Compare the screen with SCR-PM-03 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -29178,17 +29178,17 @@
       </c>
       <c r="F248" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H248" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
 3. Compare the screen with SCR-PM-04 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -29262,17 +29262,17 @@
       </c>
       <c r="F249" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H249" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
 3. Compare the screen with SCR-PM-05 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -29346,17 +29346,17 @@
       </c>
       <c r="F250" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H250" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
 3. Compare the screen with SCR-PM-06 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -29430,17 +29430,17 @@
       </c>
       <c r="F251" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H251" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
 3. Compare the screen with SCR-PM-07 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -29514,17 +29514,17 @@
       </c>
       <c r="F252" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G252" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H252" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
 3. Compare the screen with SCR-PM-08 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -29598,17 +29598,17 @@
       </c>
       <c r="F253" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G253" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H253" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu.
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Client &amp; Policy › Product Maintenance › TSU Workbench.
 3. Compare the screen with SCR-PM-09 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.</t>
@@ -29680,17 +29680,17 @@
       </c>
       <c r="F254" s="12" t="inlineStr">
         <is>
-          <t>mkttl</t>
+          <t>Marites Hernandez</t>
         </is>
       </c>
       <c r="G254" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H254" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mkttl.
+          <t>1. Sign in as Marites Hernandez (Marketing TL / TH / UH).
 2. Open Client &amp; Policy › Product Maintenance › Package Expiry.
 3. Compare the screen with SCR-PM-10 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.</t>
@@ -29762,17 +29762,17 @@
       </c>
       <c r="F255" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G255" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H255" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Products.
 3. Compare the screen with SCR-PM-11 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -29846,17 +29846,17 @@
       </c>
       <c r="F256" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G256" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H256" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Products › Product.
 3. Compare the screen with SCR-PM-12 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -29930,17 +29930,17 @@
       </c>
       <c r="F257" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G257" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H257" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Product › Package Version.
 3. Compare the screen with SCR-PM-13 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -30014,17 +30014,17 @@
       </c>
       <c r="F258" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G258" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H258" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead.
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Client &amp; Policy › Product Maintenance › Validation Queue.
 3. Compare the screen with SCR-PM-14 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -30098,17 +30098,17 @@
       </c>
       <c r="F259" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G259" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H259" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Coverages &amp; Clauses.
 3. Compare the screen with SCR-PM-15 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -30182,17 +30182,17 @@
       </c>
       <c r="F260" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G260" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H260" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Incentive Criteria.
 3. Compare the screen with SCR-PM-16 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -30266,17 +30266,17 @@
       </c>
       <c r="F261" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G261" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H261" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs.
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Client &amp; Policy › Product Maintenance › Insurers.
 3. Compare the screen with SCR-PM-17 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -30350,17 +30350,17 @@
       </c>
       <c r="F262" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G262" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H262" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs.
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Client &amp; Policy › Product Maintenance › Insurers › Insurer.
 3. Compare the screen with SCR-PM-18 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -30434,17 +30434,17 @@
       </c>
       <c r="F263" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G263" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H263" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs.
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Client &amp; Policy › Product Maintenance › Rates &amp; Taxes.
 3. Compare the screen with SCR-PM-19 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -30514,17 +30514,17 @@
       </c>
       <c r="F264" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G264" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H264" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs.
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Client &amp; Policy › Product Maintenance › Sales Organisation.
 3. Compare the screen with SCR-PM-20 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -30598,17 +30598,17 @@
       </c>
       <c r="F265" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G265" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H265" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Premium Calculator.
 3. Compare the screen with SCR-PM-21 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -30682,17 +30682,17 @@
       </c>
       <c r="F266" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G266" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H266" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Quotation / Proposal › Quotations › Quotation.
 3. Compare the screen with SCR-PM-22 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -30766,17 +30766,17 @@
       </c>
       <c r="F267" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G267" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H267" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Product Maintenance Dashboard.
 3. Compare the screen with SCR-PM-23 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -30850,17 +30850,17 @@
       </c>
       <c r="F268" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G268" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H268" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Deactivation Requests.
 3. Compare the screen with SCR-PM-24 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -30934,17 +30934,17 @@
       </c>
       <c r="F269" s="12" t="inlineStr">
         <is>
-          <t>mkttl</t>
+          <t>Marites Hernandez</t>
         </is>
       </c>
       <c r="G269" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H269" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mkttl.
+          <t>1. Sign in as Marites Hernandez (Marketing TL / TH / UH).
 2. Open Client &amp; Policy › Product Maintenance › Product Master Transfers.
 3. Compare the screen with SCR-PM-25 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.</t>
@@ -31016,17 +31016,17 @@
       </c>
       <c r="F270" s="12" t="inlineStr">
         <is>
-          <t>mkttl</t>
+          <t>Marites Hernandez</t>
         </is>
       </c>
       <c r="G270" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H270" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mkttl.
+          <t>1. Sign in as Marites Hernandez (Marketing TL / TH / UH).
 2. Open Client &amp; Policy › Product Maintenance › Placement Update Reports.
 3. Compare the screen with SCR-PM-26 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -31100,17 +31100,17 @@
       </c>
       <c r="F271" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G271" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H271" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Audit Logs.
 3. Compare the screen with SCR-PM-27 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -31184,17 +31184,17 @@
       </c>
       <c r="F272" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G272" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H272" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Product Maintenance Home › Proposal Request.
 3. Compare the screen with SCR-PM-28 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -31268,17 +31268,17 @@
       </c>
       <c r="F273" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G273" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H273" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
 3. Compare the screen with SCR-PM-29 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -31352,17 +31352,17 @@
       </c>
       <c r="F274" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G274" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H274" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Package Requests.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -31432,17 +31432,17 @@
       </c>
       <c r="F275" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G275" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H275" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › New Package Request.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -31528,17 +31528,17 @@
       </c>
       <c r="F276" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G276" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H276" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -31616,17 +31616,17 @@
       </c>
       <c r="F277" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G277" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H277" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -31722,17 +31722,17 @@
       </c>
       <c r="F278" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G278" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H278" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -31808,17 +31808,17 @@
       </c>
       <c r="F279" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G279" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H279" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -31890,17 +31890,17 @@
       </c>
       <c r="F280" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G280" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H280" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Package Requests › Package Request.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -31986,17 +31986,17 @@
       </c>
       <c r="F281" s="12" t="inlineStr">
         <is>
-          <t>mkttl</t>
+          <t>Marites Hernandez</t>
         </is>
       </c>
       <c r="G281" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H281" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mkttl.
+          <t>1. Sign in as Marites Hernandez (Marketing TL / TH / UH).
 2. Open Client &amp; Policy › Product Maintenance › Package Expiry.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -32068,17 +32068,17 @@
       </c>
       <c r="F282" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G282" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H282" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Products.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -32162,17 +32162,17 @@
       </c>
       <c r="F283" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G283" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H283" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Products › Product.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -32247,17 +32247,17 @@
       </c>
       <c r="F284" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G284" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H284" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Product › Package Version.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -32350,17 +32350,17 @@
       </c>
       <c r="F285" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G285" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H285" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Coverages &amp; Clauses.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -32440,17 +32440,17 @@
       </c>
       <c r="F286" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G286" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H286" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Incentive Criteria.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -32538,17 +32538,17 @@
       </c>
       <c r="F287" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G287" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H287" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs.
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Client &amp; Policy › Product Maintenance › Insurers.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -32628,17 +32628,17 @@
       </c>
       <c r="F288" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G288" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H288" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs.
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Client &amp; Policy › Product Maintenance › Rates &amp; Taxes.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -32710,17 +32710,17 @@
       </c>
       <c r="F289" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G289" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H289" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs.
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Client &amp; Policy › Product Maintenance › Sales Organisation.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -32802,17 +32802,17 @@
       </c>
       <c r="F290" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G290" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H290" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Product Maintenance › Premium Calculator.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -32893,17 +32893,17 @@
       </c>
       <c r="F291" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G291" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H291" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Quotation / Proposal › Quotations › Quotation.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -32976,17 +32976,17 @@
       </c>
       <c r="F292" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G292" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H292" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Any Product Maintenance record.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -33052,17 +33052,17 @@
       </c>
       <c r="F293" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G293" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H293" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Any Product Maintenance record.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -33194,17 +33194,17 @@
       </c>
       <c r="F294" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G294" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H294" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Any Product Maintenance record.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -33280,12 +33280,12 @@
       </c>
       <c r="F295" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G295" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-02 Clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="H295" s="12" t="inlineStr">
@@ -33361,12 +33361,12 @@
       </c>
       <c r="F296" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G296" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-02 Clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="H296" s="12" t="inlineStr">
@@ -33443,12 +33443,12 @@
       </c>
       <c r="F297" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G297" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-02 Clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="H297" s="12" t="inlineStr">
@@ -33525,12 +33525,12 @@
       </c>
       <c r="F298" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G298" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-02 Clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="H298" s="12" t="inlineStr">
@@ -33607,12 +33607,12 @@
       </c>
       <c r="F299" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G299" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-02 Clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="H299" s="12" t="inlineStr">
@@ -33689,17 +33689,17 @@
       </c>
       <c r="F300" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G300" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H300" s="12" t="inlineStr">
         <is>
-          <t>1. As ao send a direct request to update PRF-2026-900003 (WITH_TSU).</t>
+          <t>1. As Aileen Torres (Marketing AO) send a direct request to update PRF-2026-900003 (WITH_TSU).</t>
         </is>
       </c>
       <c r="I300" s="12" t="inlineStr">
@@ -33771,17 +33771,17 @@
       </c>
       <c r="F301" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G301" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H301" s="12" t="inlineStr">
         <is>
-          <t>1. As ao open PRF-2026-900002 and send a direct request to approve it.</t>
+          <t>1. As Aileen Torres (Marketing AO) open PRF-2026-900002 and send a direct request to approve it.</t>
         </is>
       </c>
       <c r="I301" s="12" t="inlineStr">
@@ -33853,18 +33853,18 @@
       </c>
       <c r="F302" s="12" t="inlineStr">
         <is>
-          <t>mkttl</t>
+          <t>Marites Hernandez</t>
         </is>
       </c>
       <c r="G302" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H302" s="12" t="inlineStr">
         <is>
-          <t>1. As mkttl open PRF-2026-900002; click Approve and send to TSU.
-2. As tsu open the TSU Workbench.</t>
+          <t>1. As Marites Hernandez (Marketing TL / TH / UH) open PRF-2026-900002; click Approve and send to TSU.
+2. As Teodoro Valdez (TSU Officer) open the TSU Workbench.</t>
         </is>
       </c>
       <c r="I302" s="12" t="inlineStr">
@@ -33935,12 +33935,12 @@
       </c>
       <c r="F303" s="12" t="inlineStr">
         <is>
-          <t>mkttl</t>
+          <t>Marites Hernandez</t>
         </is>
       </c>
       <c r="G303" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H303" s="12" t="inlineStr">
@@ -34017,17 +34017,17 @@
       </c>
       <c r="F304" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G304" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H304" s="12" t="inlineStr">
         <is>
-          <t>1. As tsu open the TSU Workbench; filter stage Received by TSU; search PRF-2026-900003.</t>
+          <t>1. As Teodoro Valdez (TSU Officer) open the TSU Workbench; filter stage Received by TSU; search PRF-2026-900003.</t>
         </is>
       </c>
       <c r="I304" s="12" t="inlineStr">
@@ -34098,18 +34098,18 @@
       </c>
       <c r="F305" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G305" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H305" s="12" t="inlineStr">
         <is>
           <t>1. Open PRF-2026-900003; click Return to Marketing; reason Missing supporting documents; confirm.
-2. As ao open Proposal Requests, Drafts.</t>
+2. As Aileen Torres (Marketing AO) open Proposal Requests, Drafts.</t>
         </is>
       </c>
       <c r="I305" s="12" t="inlineStr">
@@ -34119,7 +34119,7 @@
       </c>
       <c r="J305" s="12" t="inlineStr">
         <is>
-          <t>The PRF is DRAFT with the reason; ao can update and resubmit it.</t>
+          <t>The PRF is DRAFT with the reason; Aileen Torres (Marketing AO) can update and resubmit it.</t>
         </is>
       </c>
       <c r="K305" s="12" t="inlineStr">
@@ -34180,12 +34180,12 @@
       </c>
       <c r="F306" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G306" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H306" s="12" t="inlineStr">
@@ -34262,12 +34262,12 @@
       </c>
       <c r="F307" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G307" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H307" s="12" t="inlineStr">
@@ -34282,7 +34282,7 @@
       </c>
       <c r="J307" s="12" t="inlineStr">
         <is>
-          <t>The PRF is in QS_PREPARATION and the change is saved with tsu in the history.</t>
+          <t>The PRF is in QS_PREPARATION and the change is saved with Teodoro Valdez (TSU Officer) in the history.</t>
         </is>
       </c>
       <c r="K307" s="12" t="inlineStr">
@@ -34343,12 +34343,12 @@
       </c>
       <c r="F308" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G308" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H308" s="12" t="inlineStr">
@@ -34425,17 +34425,17 @@
       </c>
       <c r="F309" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G309" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF); TD-NB-03 Catalogue, insurers and TSU rules</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF); TD-NB-03 Catalogue, insurers and TSU rules</t>
         </is>
       </c>
       <c r="H309" s="12" t="inlineStr">
         <is>
-          <t>1. As tsu select INS-MGIC and INS-LAC; Submit quotation slip; then click Approve and send to insurers.</t>
+          <t>1. As Teodoro Valdez (TSU Officer) select INS-MGIC and INS-LAC; Submit quotation slip; then click Approve and send to insurers.</t>
         </is>
       </c>
       <c r="I309" s="12" t="inlineStr">
@@ -34445,7 +34445,7 @@
       </c>
       <c r="J309" s="12" t="inlineStr">
         <is>
-          <t>The slip gets QS-2026-nnnnnn; tsu's approval is refused.
+          <t>The slip gets QS-2026-nnnnnn; Teodoro Valdez (TSU Officer)'s approval is refused.
 Message "The quotation slip is approved by another TSU officer" (QS_FOUR_EYES).</t>
         </is>
       </c>
@@ -34507,17 +34507,17 @@
       </c>
       <c r="F310" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G310" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF); TD-NB-03 Catalogue, insurers and TSU rules</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF); TD-NB-03 Catalogue, insurers and TSU rules</t>
         </is>
       </c>
       <c r="H310" s="12" t="inlineStr">
         <is>
-          <t>1. As tsulead click Approve and send to insurers; open the E-mails tab.</t>
+          <t>1. As Teresa Villareal (TSU Team Lead) click Approve and send to insurers; open the E-mails tab.</t>
         </is>
       </c>
       <c r="I310" s="12" t="inlineStr">
@@ -34588,12 +34588,12 @@
       </c>
       <c r="F311" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G311" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF); TD-NB-03 Catalogue, insurers and TSU rules</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF); TD-NB-03 Catalogue, insurers and TSU rules</t>
         </is>
       </c>
       <c r="H311" s="12" t="inlineStr">
@@ -34670,18 +34670,18 @@
       </c>
       <c r="F312" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="G312" s="12" t="inlineStr">
         <is>
           <t>The test lead removes the placement e-mail of INS-MPI in SIT.
-Data: TD-NB-05 Seed proposal requests (PRF); TD-NB-03 Catalogue, insurers and TSU rules</t>
+Data: TD-NB-05 Proposal requests (PRF); TD-NB-03 Catalogue, insurers and TSU rules</t>
         </is>
       </c>
       <c r="H312" s="12" t="inlineStr">
         <is>
-          <t>1. As tsulead approve a slip addressed to INS-MPI.</t>
+          <t>1. As Teresa Villareal (TSU Team Lead) approve a slip addressed to INS-MPI.</t>
         </is>
       </c>
       <c r="I312" s="12" t="inlineStr">
@@ -34753,12 +34753,12 @@
       </c>
       <c r="F313" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G313" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF); TD-NB-03 Catalogue, insurers and TSU rules</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF); TD-NB-03 Catalogue, insurers and TSU rules</t>
         </is>
       </c>
       <c r="H313" s="12" t="inlineStr">
@@ -34835,12 +34835,12 @@
       </c>
       <c r="F314" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G314" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H314" s="12" t="inlineStr">
@@ -34917,12 +34917,12 @@
       </c>
       <c r="F315" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G315" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H315" s="12" t="inlineStr">
@@ -34998,12 +34998,12 @@
       </c>
       <c r="F316" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G316" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H316" s="12" t="inlineStr">
@@ -35080,12 +35080,12 @@
       </c>
       <c r="F317" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G317" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H317" s="12" t="inlineStr">
@@ -35162,12 +35162,12 @@
       </c>
       <c r="F318" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G318" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H318" s="12" t="inlineStr">
@@ -35244,12 +35244,12 @@
       </c>
       <c r="F319" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G319" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H319" s="12" t="inlineStr">
@@ -35325,12 +35325,12 @@
       </c>
       <c r="F320" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G320" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H320" s="12" t="inlineStr">
@@ -35406,12 +35406,12 @@
       </c>
       <c r="F321" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G321" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H321" s="12" t="inlineStr">
@@ -35487,17 +35487,17 @@
       </c>
       <c r="F322" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G322" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H322" s="12" t="inlineStr">
         <is>
-          <t>1. As ao open PRF-2026-900004; send a direct request to change a response.</t>
+          <t>1. As Aileen Torres (Marketing AO) open PRF-2026-900004; send a direct request to change a response.</t>
         </is>
       </c>
       <c r="I322" s="12" t="inlineStr">
@@ -35569,17 +35569,17 @@
       </c>
       <c r="F323" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G323" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H323" s="12" t="inlineStr">
         <is>
-          <t>1. On PRF-2026-900004 as tsu choose INS-LAC; Submit proposal slip; click Approve and release to Marketing.</t>
+          <t>1. On PRF-2026-900004 as Teodoro Valdez (TSU Officer) choose INS-LAC; Submit proposal slip; click Approve and release to Marketing.</t>
         </is>
       </c>
       <c r="I323" s="12" t="inlineStr">
@@ -35651,17 +35651,17 @@
       </c>
       <c r="F324" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G324" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H324" s="12" t="inlineStr">
         <is>
-          <t>1. As tsulead click Approve and release to Marketing.</t>
+          <t>1. As Teresa Villareal (TSU Team Lead) click Approve and release to Marketing.</t>
         </is>
       </c>
       <c r="I324" s="12" t="inlineStr">
@@ -35671,7 +35671,7 @@
       </c>
       <c r="J324" s="12" t="inlineStr">
         <is>
-          <t>The PRF is PS_RELEASED; the proposal slip PS-2026-nnnnnn is available to ao.</t>
+          <t>The PRF is PS_RELEASED; the proposal slip PS-2026-nnnnnn is available to Aileen Torres (Marketing AO).</t>
         </is>
       </c>
       <c r="K324" s="12" t="inlineStr">
@@ -35732,17 +35732,17 @@
       </c>
       <c r="F325" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G325" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H325" s="12" t="inlineStr">
         <is>
-          <t>1. As tsulead click Return for correction with a reason; as tsu submit again; open Archived versions.</t>
+          <t>1. As Teresa Villareal (TSU Team Lead) click Return for correction with a reason; as Teodoro Valdez (TSU Officer) submit again; open Archived versions.</t>
         </is>
       </c>
       <c r="I325" s="12" t="inlineStr">
@@ -35813,12 +35813,12 @@
       </c>
       <c r="F326" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G326" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H326" s="12" t="inlineStr">
@@ -35895,12 +35895,12 @@
       </c>
       <c r="F327" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G327" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF)</t>
         </is>
       </c>
       <c r="H327" s="12" t="inlineStr">
@@ -35977,12 +35977,12 @@
       </c>
       <c r="F328" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G328" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF); TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF); TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="H328" s="12" t="inlineStr">
@@ -36059,12 +36059,12 @@
       </c>
       <c r="F329" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G329" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF); TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF); TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="H329" s="12" t="inlineStr">
@@ -36141,12 +36141,12 @@
       </c>
       <c r="F330" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G330" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Seed proposal requests (PRF); TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-05 Proposal requests (PRF); TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="H330" s="12" t="inlineStr">
@@ -36223,13 +36223,13 @@
       </c>
       <c r="F331" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G331" s="12" t="inlineStr">
         <is>
           <t>An accepted PRF of prospect PR-2026-000008 (Bayside Builders Co.).
-Data: TD-NB-05 Seed proposal requests (PRF); TD-NB-12 Documents to upload</t>
+Data: TD-NB-05 Proposal requests (PRF); TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="H331" s="12" t="inlineStr">
@@ -36306,12 +36306,12 @@
       </c>
       <c r="F332" s="12" t="inlineStr">
         <is>
-          <t>mkttl</t>
+          <t>Marites Hernandez</t>
         </is>
       </c>
       <c r="G332" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Seed placement and billing</t>
+          <t>Data: TD-NB-07 Placement and billing</t>
         </is>
       </c>
       <c r="H332" s="12" t="inlineStr">
@@ -36387,12 +36387,12 @@
       </c>
       <c r="F333" s="12" t="inlineStr">
         <is>
-          <t>mkttl</t>
+          <t>Marites Hernandez</t>
         </is>
       </c>
       <c r="G333" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Seed placement and billing</t>
+          <t>Data: TD-NB-07 Placement and billing</t>
         </is>
       </c>
       <c r="H333" s="12" t="inlineStr">
@@ -36468,17 +36468,17 @@
       </c>
       <c r="F334" s="12" t="inlineStr">
         <is>
-          <t>badmin</t>
+          <t>Bea Garcia</t>
         </is>
       </c>
       <c r="G334" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Seed placement and billing</t>
+          <t>Data: TD-NB-07 Placement and billing</t>
         </is>
       </c>
       <c r="H334" s="12" t="inlineStr">
         <is>
-          <t>1. As badmin run NB-PLC-UPDATE.</t>
+          <t>1. As Bea Garcia (Business Administrator) run NB-PLC-UPDATE.</t>
         </is>
       </c>
       <c r="I334" s="12" t="inlineStr">
@@ -36550,7 +36550,7 @@
       </c>
       <c r="F335" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G335" s="12" t="inlineStr">
@@ -36560,7 +36560,7 @@
       </c>
       <c r="H335" s="12" t="inlineStr">
         <is>
-          <t>1. As ao open New Business Reports; run NB-CLPC-BILLING by a direct request.</t>
+          <t>1. As Aileen Torres (Marketing AO) open New Business Reports; run NB-CLPC-BILLING by a direct request.</t>
         </is>
       </c>
       <c r="I335" s="12" t="inlineStr">
@@ -36632,7 +36632,7 @@
       </c>
       <c r="F336" s="12" t="inlineStr">
         <is>
-          <t>mkttl</t>
+          <t>Marites Hernandez</t>
         </is>
       </c>
       <c r="G336" s="12" t="inlineStr">
@@ -36713,7 +36713,7 @@
       </c>
       <c r="F337" s="12" t="inlineStr">
         <is>
-          <t>mkttl</t>
+          <t>Marites Hernandez</t>
         </is>
       </c>
       <c r="G337" s="12" t="inlineStr">
@@ -36795,17 +36795,17 @@
       </c>
       <c r="F338" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G338" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H338" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Non-Package Management › Proposal Requests.
 3. Compare the screen with SCR-NB-09 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.</t>
@@ -36877,17 +36877,17 @@
       </c>
       <c r="F339" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G339" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H339" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Non-Package Management › New Proposal Request.
 3. Compare the screen with SCR-NB-10 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -36961,17 +36961,17 @@
       </c>
       <c r="F340" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G340" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H340" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Non-Package Management › Proposal Requests › Proposal Request.
 3. Compare the screen with SCR-NB-11 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -37045,17 +37045,17 @@
       </c>
       <c r="F341" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G341" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H341" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu.
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Client &amp; Policy › Non-Package Management › TSU Workbench.
 3. Compare the screen with SCR-NB-12 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.</t>
@@ -37127,17 +37127,17 @@
       </c>
       <c r="F342" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G342" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H342" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Reports › New Business Reports › New Business Reports.
 3. Compare the screen with SCR-NB-40 in the FRS: the fields, their order, labels, types, mandatory markers, defaults and lists.
 4. Check the buttons offered to the persona and when each is enabled.
@@ -37211,17 +37211,17 @@
       </c>
       <c r="F343" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G343" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H343" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Non-Package Management › New Proposal Request.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -37304,17 +37304,17 @@
       </c>
       <c r="F344" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G344" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H344" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Client &amp; Policy › Non-Package Management › Proposal Requests › Proposal Request.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -37404,17 +37404,17 @@
       </c>
       <c r="F345" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G345" s="12" t="inlineStr">
         <is>
-          <t>Seed data of the SIT environment.</t>
+          <t>Test data prepared for the walkthrough.</t>
         </is>
       </c>
       <c r="H345" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao.
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Reports › New Business Reports › New Business Reports.
 3. For each message listed, create the condition described in the messages catalogue of the FRS (chapter 15) and run the action.</t>
         </is>
@@ -37488,17 +37488,17 @@
       </c>
       <c r="F346" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G346" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H346" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Product Maintenance &gt; Product Maintenance Home.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -37572,17 +37572,17 @@
       </c>
       <c r="F347" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G347" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H347" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Product Maintenance &gt; Product Maintenance Home.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -37656,17 +37656,17 @@
       </c>
       <c r="F348" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G348" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H348" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Product Maintenance &gt; Product Maintenance Home.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -37740,17 +37740,17 @@
       </c>
       <c r="F349" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G349" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H349" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao (Marketing AO).
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Product Maintenance &gt; Product Maintenance Home.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -37824,17 +37824,17 @@
       </c>
       <c r="F350" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G350" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H350" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao (Marketing AO).
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Product Maintenance &gt; Product Maintenance Home.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -37908,17 +37908,17 @@
       </c>
       <c r="F351" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G351" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H351" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -37992,17 +37992,17 @@
       </c>
       <c r="F352" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G352" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H352" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -38076,17 +38076,17 @@
       </c>
       <c r="F353" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G353" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H353" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Products.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -38160,17 +38160,17 @@
       </c>
       <c r="F354" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G354" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H354" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Products.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -38244,17 +38244,17 @@
       </c>
       <c r="F355" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G355" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H355" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Products &gt; Product page.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -38328,17 +38328,17 @@
       </c>
       <c r="F356" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G356" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H356" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Products &gt; Product page.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -38412,17 +38412,17 @@
       </c>
       <c r="F357" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G357" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H357" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Products &gt; Product page.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -38496,17 +38496,17 @@
       </c>
       <c r="F358" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G358" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H358" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Product Maintenance &gt; Products &gt; Product page.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -38580,17 +38580,17 @@
       </c>
       <c r="F359" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G359" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H359" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Product Maintenance &gt; Products &gt; Product page.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -38664,17 +38664,17 @@
       </c>
       <c r="F360" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G360" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H360" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Product Maintenance &gt; Products &gt; Product page.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -38748,17 +38748,17 @@
       </c>
       <c r="F361" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G361" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H361" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page (workflow panel).
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -38832,17 +38832,17 @@
       </c>
       <c r="F362" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G362" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H362" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page (workflow panel).
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -38921,7 +38921,7 @@
       </c>
       <c r="G363" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H363" s="12" t="inlineStr">
@@ -39004,7 +39004,7 @@
       </c>
       <c r="G364" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H364" s="12" t="inlineStr">
@@ -39087,7 +39087,7 @@
       </c>
       <c r="G365" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H365" s="12" t="inlineStr">
@@ -39165,17 +39165,17 @@
       </c>
       <c r="F366" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G366" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H366" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Product Maintenance &gt; Package Requests.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -39249,17 +39249,17 @@
       </c>
       <c r="F367" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G367" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H367" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page (workflow panel).
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -39333,17 +39333,17 @@
       </c>
       <c r="F368" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G368" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H368" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page (workflow panel).
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -39417,17 +39417,17 @@
       </c>
       <c r="F369" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G369" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H369" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Coverages &amp; Clauses &gt; Field Rules.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -39501,17 +39501,17 @@
       </c>
       <c r="F370" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G370" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H370" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Coverages &amp; Clauses &gt; Field Rules.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -39585,17 +39585,17 @@
       </c>
       <c r="F371" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G371" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H371" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Coverages &amp; Clauses &gt; Field Rules.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -39674,7 +39674,7 @@
       </c>
       <c r="G372" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H372" s="12" t="inlineStr">
@@ -39757,7 +39757,7 @@
       </c>
       <c r="G373" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H373" s="12" t="inlineStr">
@@ -39835,17 +39835,17 @@
       </c>
       <c r="F374" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G374" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H374" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao (Marketing AO).
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open New Business &gt; Proposal Requests.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -39919,17 +39919,17 @@
       </c>
       <c r="F375" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G375" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H375" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao (Marketing AO).
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open New Business &gt; Proposal Requests.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -40003,17 +40003,17 @@
       </c>
       <c r="F376" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G376" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H376" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao (Marketing AO).
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open New Business &gt; Proposal Requests.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -40087,17 +40087,17 @@
       </c>
       <c r="F377" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G377" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H377" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsulead (TSU Team Lead).
+          <t>1. Sign in as Teresa Villareal (TSU Team Lead).
 2. Open New Business &gt; Proposal Requests &gt; TSU Workbench.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -40171,17 +40171,17 @@
       </c>
       <c r="F378" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G378" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H378" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsulead (TSU Team Lead).
+          <t>1. Sign in as Teresa Villareal (TSU Team Lead).
 2. Open New Business &gt; Proposal Requests &gt; TSU Workbench.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -40255,17 +40255,17 @@
       </c>
       <c r="F379" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G379" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H379" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open New Business &gt; Proposal Requests &gt; Quotation Slips.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -40339,17 +40339,17 @@
       </c>
       <c r="F380" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G380" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H380" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open New Business &gt; Proposal Requests &gt; Quotation Slips.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -40423,17 +40423,17 @@
       </c>
       <c r="F381" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G381" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H381" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open New Business &gt; Proposal Requests &gt; Quotation Slips.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -40507,17 +40507,17 @@
       </c>
       <c r="F382" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G382" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H382" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open New Business &gt; Proposal Requests &gt; Comparative Table.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -40591,17 +40591,17 @@
       </c>
       <c r="F383" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G383" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H383" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open New Business &gt; Proposal Requests &gt; Comparative Table.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -40675,17 +40675,17 @@
       </c>
       <c r="F384" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G384" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H384" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open New Business &gt; Proposal Requests &gt; Comparative Table.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -40759,17 +40759,17 @@
       </c>
       <c r="F385" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G385" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H385" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Reports &gt; Placement Update Report.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -40843,17 +40843,17 @@
       </c>
       <c r="F386" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G386" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H386" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Reports &gt; Placement Update Report.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -40927,17 +40927,17 @@
       </c>
       <c r="F387" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G387" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H387" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Reports &gt; Placement Update Report.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -41011,17 +41011,17 @@
       </c>
       <c r="F388" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G388" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H388" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Reports &gt; Package Status Update Report.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -41095,17 +41095,17 @@
       </c>
       <c r="F389" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G389" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H389" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Reports &gt; Package Status Update Report.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -41179,17 +41179,17 @@
       </c>
       <c r="F390" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G390" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H390" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao (Marketing AO).
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open New Business &gt; Proposal Requests &gt; Comparative Table.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -41263,17 +41263,17 @@
       </c>
       <c r="F391" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G391" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H391" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao (Marketing AO).
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open New Business &gt; Proposal Requests &gt; Comparative Table.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -41347,17 +41347,17 @@
       </c>
       <c r="F392" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G392" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H392" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open New Business &gt; Proposal Requests &gt; Proposal.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -41431,17 +41431,17 @@
       </c>
       <c r="F393" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G393" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H393" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open New Business &gt; Proposal Requests &gt; Proposal.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -41515,17 +41515,17 @@
       </c>
       <c r="F394" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G394" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H394" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open New Business &gt; Proposal Requests &gt; Proposal.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -41599,17 +41599,17 @@
       </c>
       <c r="F395" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G395" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H395" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao (Marketing AO).
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open New Business &gt; Proposal Requests &gt; Client response.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -41683,17 +41683,17 @@
       </c>
       <c r="F396" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G396" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H396" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao (Marketing AO).
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open New Business &gt; Proposal Requests &gt; Client response.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -41767,17 +41767,17 @@
       </c>
       <c r="F397" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G397" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H397" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao (Marketing AO).
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open New Business &gt; Proposal Requests &gt; Client response.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -41851,17 +41851,17 @@
       </c>
       <c r="F398" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G398" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H398" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsulead (TSU Team Lead).
+          <t>1. Sign in as Teresa Villareal (TSU Team Lead).
 2. Open Product Maintenance &gt; Package Requests.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -41935,17 +41935,17 @@
       </c>
       <c r="F399" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G399" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H399" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsulead (TSU Team Lead).
+          <t>1. Sign in as Teresa Villareal (TSU Team Lead).
 2. Open Product Maintenance &gt; Package Requests.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -42019,17 +42019,17 @@
       </c>
       <c r="F400" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G400" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H400" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao (Marketing AO).
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Product Maintenance &gt; Package Requests &gt; New Package Request.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -42103,17 +42103,17 @@
       </c>
       <c r="F401" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G401" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H401" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao (Marketing AO).
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Product Maintenance &gt; Package Requests &gt; New Package Request.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -42187,17 +42187,17 @@
       </c>
       <c r="F402" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G402" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H402" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao (Marketing AO).
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Product Maintenance &gt; Package Requests &gt; New Package Request.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -42271,17 +42271,17 @@
       </c>
       <c r="F403" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G403" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H403" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao (Marketing AO).
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Product Maintenance &gt; Package Requests &gt; New Package Request.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -42355,17 +42355,17 @@
       </c>
       <c r="F404" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G404" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H404" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao (Marketing AO).
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open Product Maintenance &gt; Package Requests &gt; New Package Request.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -42439,17 +42439,17 @@
       </c>
       <c r="F405" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G405" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H405" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsulead (TSU Team Lead).
+          <t>1. Sign in as Teresa Villareal (TSU Team Lead).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page (workflow panel).
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -42523,17 +42523,17 @@
       </c>
       <c r="F406" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G406" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H406" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsulead (TSU Team Lead).
+          <t>1. Sign in as Teresa Villareal (TSU Team Lead).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page (workflow panel).
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -42607,17 +42607,17 @@
       </c>
       <c r="F407" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G407" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H407" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Negotiation tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -42691,17 +42691,17 @@
       </c>
       <c r="F408" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G408" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H408" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Negotiation tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -42775,17 +42775,17 @@
       </c>
       <c r="F409" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G409" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H409" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Negotiation tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -42859,17 +42859,17 @@
       </c>
       <c r="F410" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G410" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H410" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Negotiation tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -42943,17 +42943,17 @@
       </c>
       <c r="F411" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G411" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H411" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Negotiation tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -43027,17 +43027,17 @@
       </c>
       <c r="F412" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G412" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H412" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Negotiation tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -43111,17 +43111,17 @@
       </c>
       <c r="F413" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G413" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H413" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Negotiation tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -43195,17 +43195,17 @@
       </c>
       <c r="F414" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G414" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H414" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Negotiation tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -43279,17 +43279,17 @@
       </c>
       <c r="F415" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G415" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H415" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Negotiation tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -43363,17 +43363,17 @@
       </c>
       <c r="F416" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G416" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H416" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Negotiation tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -43447,17 +43447,17 @@
       </c>
       <c r="F417" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G417" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H417" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Comparative tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -43531,17 +43531,17 @@
       </c>
       <c r="F418" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G418" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H418" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Comparative tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -43615,17 +43615,17 @@
       </c>
       <c r="F419" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G419" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H419" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Comparative tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -43699,17 +43699,17 @@
       </c>
       <c r="F420" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G420" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H420" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Negotiation tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -43783,17 +43783,17 @@
       </c>
       <c r="F421" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G421" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H421" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Negotiation tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -43867,17 +43867,17 @@
       </c>
       <c r="F422" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G422" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H422" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page (workflow panel).
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -43951,17 +43951,17 @@
       </c>
       <c r="F423" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G423" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H423" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page (workflow panel).
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -44035,17 +44035,17 @@
       </c>
       <c r="F424" s="12" t="inlineStr">
         <is>
-          <t>mancom</t>
+          <t>Manuel Uy</t>
         </is>
       </c>
       <c r="G424" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H424" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mancom (ManCom member).
+          <t>1. Sign in as Manuel Uy (ManCom member).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Requirements &amp; Sign-off tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -44119,17 +44119,17 @@
       </c>
       <c r="F425" s="12" t="inlineStr">
         <is>
-          <t>mancom</t>
+          <t>Manuel Uy</t>
         </is>
       </c>
       <c r="G425" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H425" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mancom (ManCom member).
+          <t>1. Sign in as Manuel Uy (ManCom member).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Requirements &amp; Sign-off tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -44203,17 +44203,17 @@
       </c>
       <c r="F426" s="12" t="inlineStr">
         <is>
-          <t>mancom</t>
+          <t>Manuel Uy</t>
         </is>
       </c>
       <c r="G426" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H426" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mancom (ManCom member).
+          <t>1. Sign in as Manuel Uy (ManCom member).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Requirements &amp; Sign-off tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -44287,17 +44287,17 @@
       </c>
       <c r="F427" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G427" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H427" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Requirements &amp; Sign-off tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -44371,17 +44371,17 @@
       </c>
       <c r="F428" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G428" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H428" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Requirements &amp; Sign-off tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -44455,17 +44455,17 @@
       </c>
       <c r="F429" s="12" t="inlineStr">
         <is>
-          <t>mancom</t>
+          <t>Manuel Uy</t>
         </is>
       </c>
       <c r="G429" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H429" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mancom (ManCom member).
+          <t>1. Sign in as Manuel Uy (ManCom member).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Requirements &amp; Sign-off tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -44539,17 +44539,17 @@
       </c>
       <c r="F430" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G430" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H430" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Set-up tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -44623,17 +44623,17 @@
       </c>
       <c r="F431" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G431" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H431" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Product Maintenance &gt; Validation Queue.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -44707,17 +44707,17 @@
       </c>
       <c r="F432" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G432" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H432" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Product Maintenance &gt; Validation Queue.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -44791,17 +44791,17 @@
       </c>
       <c r="F433" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G433" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H433" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Product Maintenance &gt; Validation Queue.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -44875,17 +44875,17 @@
       </c>
       <c r="F434" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G434" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H434" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Product Maintenance &gt; Validation Queue.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -44959,17 +44959,17 @@
       </c>
       <c r="F435" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G435" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H435" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsulead (TSU Team Lead).
+          <t>1. Sign in as Teresa Villareal (TSU Team Lead).
 2. Open Product Maintenance &gt; TSU Workbench.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -45043,17 +45043,17 @@
       </c>
       <c r="F436" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G436" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H436" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Incentive Criteria.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -45127,17 +45127,17 @@
       </c>
       <c r="F437" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G437" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H437" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Incentive Criteria.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -45211,17 +45211,17 @@
       </c>
       <c r="F438" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G438" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H438" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Incentive Criteria.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -45300,7 +45300,7 @@
       </c>
       <c r="G439" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H439" s="12" t="inlineStr">
@@ -45383,7 +45383,7 @@
       </c>
       <c r="G440" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H440" s="12" t="inlineStr">
@@ -45461,17 +45461,17 @@
       </c>
       <c r="F441" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G441" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H441" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Reports &gt; Renewal Request Report.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -45545,17 +45545,17 @@
       </c>
       <c r="F442" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G442" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H442" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Reports &gt; Package Expiry Report.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -45629,17 +45629,17 @@
       </c>
       <c r="F443" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G443" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H443" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Reports &gt; Package Version History.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -45713,17 +45713,17 @@
       </c>
       <c r="F444" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G444" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H444" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Reports.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -45797,17 +45797,17 @@
       </c>
       <c r="F445" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G445" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H445" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Reports.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -45881,17 +45881,17 @@
       </c>
       <c r="F446" s="12" t="inlineStr">
         <is>
-          <t>tsuhead</t>
+          <t>Tomas Vergara</t>
         </is>
       </c>
       <c r="G446" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H446" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsuhead (TSU Head).
+          <t>1. Sign in as Tomas Vergara (TSU Head).
 2. Open Reports.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -45965,17 +45965,17 @@
       </c>
       <c r="F447" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Auditor</t>
         </is>
       </c>
       <c r="G447" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H447" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as auditor (Auditor).
+          <t>1. Sign in as the Auditor.
 2. Open Audit &gt; Audit Logs.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -46049,17 +46049,17 @@
       </c>
       <c r="F448" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Auditor</t>
         </is>
       </c>
       <c r="G448" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H448" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as auditor (Auditor).
+          <t>1. Sign in as the Auditor.
 2. Open Audit &gt; Audit Logs.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -46133,17 +46133,17 @@
       </c>
       <c r="F449" s="12" t="inlineStr">
         <is>
-          <t>auditor</t>
+          <t>Auditor</t>
         </is>
       </c>
       <c r="G449" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H449" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as auditor (Auditor).
+          <t>1. Sign in as the Auditor.
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; History tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -46217,17 +46217,17 @@
       </c>
       <c r="F450" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G450" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H450" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Coverages &amp; Clauses.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -46301,17 +46301,17 @@
       </c>
       <c r="F451" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G451" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H451" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Coverages &amp; Clauses.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -46385,17 +46385,17 @@
       </c>
       <c r="F452" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G452" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H452" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Coverages &amp; Clauses &gt; Clause Library.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -46469,17 +46469,17 @@
       </c>
       <c r="F453" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G453" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H453" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Coverages &amp; Clauses &gt; Clause Library.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -46553,17 +46553,17 @@
       </c>
       <c r="F454" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G454" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H454" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Products &gt; Package Version.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -46637,17 +46637,17 @@
       </c>
       <c r="F455" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G455" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H455" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Products &gt; Package Version.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -46721,17 +46721,17 @@
       </c>
       <c r="F456" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G456" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H456" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Products &gt; Package Version.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -46805,17 +46805,17 @@
       </c>
       <c r="F457" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G457" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H457" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Products &gt; Package Version.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -46889,17 +46889,17 @@
       </c>
       <c r="F458" s="12" t="inlineStr">
         <is>
-          <t>mbs</t>
+          <t>Monica Vergara</t>
         </is>
       </c>
       <c r="G458" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H458" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as mbs (Marketing Business Services).
+          <t>1. Sign in as Monica Vergara (Marketing Business Services).
 2. Open Product Maintenance &gt; Products &gt; Package Version.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -46973,17 +46973,17 @@
       </c>
       <c r="F459" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G459" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H459" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao (Marketing AO).
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open New Business &gt; Quotations &gt; Rate scheme panel.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -47057,17 +47057,17 @@
       </c>
       <c r="F460" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G460" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H460" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao (Marketing AO).
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open New Business &gt; Quotations &gt; Rate scheme panel.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -47141,17 +47141,17 @@
       </c>
       <c r="F461" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G461" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H461" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao (Marketing AO).
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open New Business &gt; Quotations &gt; Rate scheme panel.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -47225,17 +47225,17 @@
       </c>
       <c r="F462" s="12" t="inlineStr">
         <is>
-          <t>ao</t>
+          <t>Aileen Torres</t>
         </is>
       </c>
       <c r="G462" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H462" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as ao (Marketing AO).
+          <t>1. Sign in as Aileen Torres (Marketing AO).
 2. Open New Business &gt; Quotations &gt; Rate scheme panel.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -47309,17 +47309,17 @@
       </c>
       <c r="F463" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G463" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H463" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Advisories tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -47393,17 +47393,17 @@
       </c>
       <c r="F464" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G464" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H464" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Advisories tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -47477,17 +47477,17 @@
       </c>
       <c r="F465" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G465" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H465" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; Advisories tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -47561,17 +47561,17 @@
       </c>
       <c r="F466" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G466" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H466" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Expiry.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -47645,17 +47645,17 @@
       </c>
       <c r="F467" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G467" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H467" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Expiry.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -47729,17 +47729,17 @@
       </c>
       <c r="F468" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G468" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H468" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Expiry.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -47813,17 +47813,17 @@
       </c>
       <c r="F469" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G469" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H469" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; E-mails tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -47897,17 +47897,17 @@
       </c>
       <c r="F470" s="12" t="inlineStr">
         <is>
-          <t>tsu</t>
+          <t>Teodoro Valdez</t>
         </is>
       </c>
       <c r="G470" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H470" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsu (TSU Officer).
+          <t>1. Sign in as Teodoro Valdez (TSU Officer).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page &gt; E-mails tab.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -47986,7 +47986,7 @@
       </c>
       <c r="G471" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H471" s="12" t="inlineStr">
@@ -48069,7 +48069,7 @@
       </c>
       <c r="G472" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H472" s="12" t="inlineStr">
@@ -48147,17 +48147,17 @@
       </c>
       <c r="F473" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G473" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H473" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsulead (TSU Team Lead).
+          <t>1. Sign in as Teresa Villareal (TSU Team Lead).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page (workflow panel).
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -48231,17 +48231,17 @@
       </c>
       <c r="F474" s="12" t="inlineStr">
         <is>
-          <t>tsulead</t>
+          <t>Teresa Villareal</t>
         </is>
       </c>
       <c r="G474" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H474" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as tsulead (TSU Team Lead).
+          <t>1. Sign in as Teresa Villareal (TSU Team Lead).
 2. Open Product Maintenance &gt; Package Requests &gt; Package Request page (workflow panel).
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -48315,17 +48315,17 @@
       </c>
       <c r="F475" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="G475" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H475" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as the System Administrator.
 2. Open Setup &amp; Administration &gt; Document Templates.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
@@ -48399,17 +48399,17 @@
       </c>
       <c r="F476" s="12" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="G476" s="12" t="inlineStr">
         <is>
-          <t>SIT/UAT data of the test plan; the user holds the role of the persona</t>
+          <t>the test data prepared for the walkthrough; the user holds the role of the persona</t>
         </is>
       </c>
       <c r="H476" s="12" t="inlineStr">
         <is>
-          <t>1. Sign in as admin (System Administrator).
+          <t>1. Sign in as the System Administrator.
 2. Open Setup &amp; Administration &gt; Document Templates.
 3. Carry out the situation the criterion describes, with the test data.
 4. Compare the result with the expected result.</t>
